--- a/repair/back/doc/estimate/detail-compare2.xlsx
+++ b/repair/back/doc/estimate/detail-compare2.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhki/program/repair/back/doc/estimate/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD20112-BA6C-8F49-B5E2-E8756152BDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="7" rupBuild=""/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="1220" yWindow="500" windowWidth="39740" windowHeight="22540" xr2:uid="{3CBC3ECF-6A6D-0143-9DD2-2354645F575C}"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="1" r:id="rId1"/>
@@ -20,279 +14,204 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">갑지!$A$1:$J$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">을지!$A$1:$I$27</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t xml:space="preserve"> 용  역  명 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> 용  역  비</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>용역산출</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>항목 /구분</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>내         용</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>금  액</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>비  고</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>직접인건비(A)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>직접경비(B)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>재 경 비(C)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>기 술 료(D)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>추가경비(E)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>계  (F)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>견적금액</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>견적금액</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>기   간</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>용역범위</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>첨   부</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">산출내역 1부 </t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>항목/구분</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>내    역</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>산 출 근 거</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>연인원</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>단   가</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>금   액</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>비  고</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>내업(인)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>계</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>직접경비
 (B)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>소     계</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>기 술 료
 (D)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>소 계</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>A + B + C + D</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>추가경비
 (E)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>계</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>A + B + C + D + E</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>대   금
 지급조건</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>세   부
 용역내용</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>비   고</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>㈜지우구조기술사사무소</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>안전진단전문기관 등록업체</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>일           자</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> 수      신</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>◆산출내역</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>외업(인)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>일     비</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>차량운행비</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>숙박비</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>현지보조인부</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>위험수당</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>기계기구손료</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>보고서인쇄비</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>제 경 비
 (C)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>직접인건비
 (A)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">  1. 납품시 : 100% 현금지급</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>견   적   서</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>부가세 별도</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>e-mail:zywooeng@naver.com</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -302,50 +221,40 @@
       <rPr>
         <b/>
         <sz val="12"/>
+        <color rgb="FF000000"/>
         <rFont val="굴림체"/>
-        <family val="3"/>
-        <charset val="129"/>
       </rPr>
       <t xml:space="preserve">       김    범    진 (인)</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>A + B + C + D + E</t>
   </si>
   <si>
     <t>서울특별시 금천구 가산디지털2로 144, 606호(현대테라타워)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>TEL:(02)6956-7045 FAX:(02)6956-7046</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>착수 후 30일</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">이매촌삼환아파트 </t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>아파트 10개동 572세대 (해당동 - 8개동)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>시설물의 안전 및 유지관리에 관한 특별법 제11조의 의거 건축물 정밀안전점검</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>1. 현장조사 과정에서 마감재 및 구조체의 국부적인 철거(훼손)가 불가피 할 경우 
    발주자와 협의하여 조사부위를 선정하여 조사 후 복구는 발주자가 시행하는 조건
    으로 함.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>2025년 정밀안전점검 용역</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>특급기술자</t>
@@ -358,12 +267,15 @@
   </si>
   <si>
     <t>초급기술자</t>
+  </si>
+  <si>
+    <t>담당자 : 이명수 이사 (HP : 010-4180-8346)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="26">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
@@ -392,566 +304,1026 @@
     <numFmt numFmtId="188" formatCode="&quot;(&quot;#&quot;%):부가세포함&quot;"/>
     <numFmt numFmtId="189" formatCode="#&quot;인&quot;"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="49">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <name val="굴림체"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="8.0"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <b/>
-      <sz val="28"/>
+      <sz val="28.0"/>
       <name val="굴림체"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <name val="굴림체"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="31"/>
+      <sz val="31.0"/>
       <name val="바탕체"/>
-      <family val="1"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <name val="굴림체"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <name val="굴림체"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <name val="바탕체"/>
-      <family val="1"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="20.0"/>
       <name val="굴림체"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <name val="굴림체"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <name val="굴림체"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="9"/>
+      <sz val="11.0"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="16.0"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color indexed="63"/>
+      <sz val="10.0"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF333333"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="9.0"/>
       <name val="굴림체"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <name val="굴림체"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <name val="굴림체"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color theme="10"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color theme="11"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <name val="돋움"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="돋움"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="돋움"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color theme="3"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FF3F3F76"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FF3F3F3F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FFFA7D00"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color theme="0"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color rgb="FF7F7F7F"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="9"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799980"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599990"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399980"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="45">
+  <borders count="54">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="double">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="double">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="double">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -959,134 +1331,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
+      <bottom style="thick">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="double">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
+      <bottom style="thick">
+        <color rgb="FFACCCEA"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1095,134 +1350,310 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
+        <color theme="4" tint="0.399980"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color indexed="64"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyNumberFormat="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="7" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="0" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="45" applyAlignment="0" applyFont="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="46" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="47" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="48" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="49" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="50" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="49" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="51" applyAlignment="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="52" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="53" applyAlignment="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="11" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="14" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="16" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="17" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="18" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="19" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="20" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="21" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="22" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="23" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="24" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="26" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="27" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="28" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="29" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="30" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="31" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="32" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="33" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="34" borderId="0" applyAlignment="0" applyBorder="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="37" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1">
@@ -1234,7 +1665,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
@@ -1245,146 +1676,146 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="175" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="175" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="17" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="17" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="17" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="182" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1392,153 +1823,147 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="186" fontId="5" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="5" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="5" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="187" fontId="5" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="185" fontId="2" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="18" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="38" fontId="18" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="189" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="12" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="189" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="12" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="188" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="188" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
@@ -1556,113 +1981,101 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="18" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="18" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="183" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="183" fontId="18" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="17" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="17" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1672,7 +2085,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -1680,67 +2093,59 @@
       <alignment horizontal="right" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="180" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="180" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="180" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="180" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="180" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="180" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1748,21 +2153,58 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="50">
+    <cellStyle name="20% - 강조색1" xfId="26" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="30" builtinId="34"/>
+    <cellStyle name="20% - 강조색3" xfId="34" builtinId="38"/>
+    <cellStyle name="20% - 강조색4" xfId="38" builtinId="42"/>
+    <cellStyle name="20% - 강조색5" xfId="42" builtinId="46"/>
+    <cellStyle name="20% - 강조색6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 강조색1" xfId="27" builtinId="31"/>
+    <cellStyle name="40% - 강조색2" xfId="31" builtinId="35"/>
+    <cellStyle name="40% - 강조색3" xfId="35" builtinId="39"/>
+    <cellStyle name="40% - 강조색4" xfId="39" builtinId="43"/>
+    <cellStyle name="40% - 강조색5" xfId="43" builtinId="47"/>
+    <cellStyle name="40% - 강조색6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 강조색1" xfId="28" builtinId="32"/>
+    <cellStyle name="60% - 강조색2" xfId="32" builtinId="36"/>
+    <cellStyle name="60% - 강조색3" xfId="36" builtinId="40"/>
+    <cellStyle name="60% - 강조색4" xfId="40" builtinId="44"/>
+    <cellStyle name="60% - 강조색5" xfId="44" builtinId="48"/>
+    <cellStyle name="60% - 강조색6" xfId="48" builtinId="52"/>
     <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="표준_견적XL97" xfId="2" xr:uid="{6D3066DF-F848-D14A-9BCA-417D10A3A79F}"/>
+    <cellStyle name="강조색1" xfId="25" builtinId="29"/>
+    <cellStyle name="강조색2" xfId="29" builtinId="33"/>
+    <cellStyle name="강조색3" xfId="33" builtinId="37"/>
+    <cellStyle name="강조색4" xfId="37" builtinId="41"/>
+    <cellStyle name="강조색5" xfId="41" builtinId="45"/>
+    <cellStyle name="강조색6" xfId="45" builtinId="49"/>
+    <cellStyle name="경고문" xfId="10" builtinId="11"/>
+    <cellStyle name="계산" xfId="18" builtinId="22"/>
+    <cellStyle name="나쁨" xfId="23" builtinId="27"/>
+    <cellStyle name="메모" xfId="9" builtinId="10"/>
+    <cellStyle name="백분율" xfId="5" builtinId="5"/>
+    <cellStyle name="보통" xfId="24" builtinId="28"/>
+    <cellStyle name="설명텍스트" xfId="49" builtinId="53"/>
+    <cellStyle name="셀 확인" xfId="19" builtinId="23"/>
+    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
+    <cellStyle name="연결된 셀" xfId="20" builtinId="24"/>
+    <cellStyle name="열어본 하이퍼링크" xfId="8" builtinId="9" hidden="1"/>
+    <cellStyle name="요약" xfId="21" builtinId="25"/>
+    <cellStyle name="입력" xfId="16" builtinId="20"/>
+    <cellStyle name="제목" xfId="11" builtinId="15"/>
+    <cellStyle name="제목1" xfId="12" builtinId="16"/>
+    <cellStyle name="제목2" xfId="13" builtinId="17"/>
+    <cellStyle name="제목3" xfId="14" builtinId="18"/>
+    <cellStyle name="제목4" xfId="15" builtinId="19"/>
+    <cellStyle name="좋음" xfId="22" builtinId="26"/>
+    <cellStyle name="출력" xfId="17" builtinId="21"/>
+    <cellStyle name="통화" xfId="4" builtinId="4"/>
+    <cellStyle name="통화[0]" xfId="6" builtinId="7"/>
+    <cellStyle name="하이퍼링크" xfId="7" builtinId="8" hidden="1"/>
+    <cellStyle name="표준_견적XL97" xfId="2"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1777,13 +2219,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>990600</xdr:colOff>
+      <xdr:colOff>992505</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1064" name="그림 1046">
+        <xdr:cNvPr id="1064" name="그림 1046" descr="xl/media/image1.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{406E7B07-EEB1-67EF-FAD6-CD783EB692A8}"/>
@@ -1791,11 +2233,11 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:clrChange>
             <a:clrFrom>
               <a:srgbClr val="FFFFFF"/>
@@ -1817,37 +2259,17 @@
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="6438900" y="1943100"/>
-          <a:ext cx="774700" cy="863600"/>
+          <a:off x="7129780" y="1918335"/>
+          <a:ext cx="776604" cy="869950"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
-        <a:ln>
+        <a:ln cap="flat" cmpd="sng">
           <a:noFill/>
+          <a:prstDash/>
         </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2141,26 +2563,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48FD3C93-E9D1-664E-9F1E-5604501F20D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L951"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="7.1640625" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="7.16406250" defaultRowHeight="13.500000"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="31" customWidth="1"/>
-    <col min="2" max="2" width="3.5" style="31" customWidth="1"/>
-    <col min="3" max="3" width="5.5" style="31" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" style="31" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" style="31" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" style="32" customWidth="1"/>
-    <col min="7" max="7" width="10.5" style="31" customWidth="1"/>
-    <col min="8" max="8" width="12" style="31" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" style="31" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="7.1640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="7.1640625" style="1"/>
+    <col min="1" max="1" style="31" width="2.67166660" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="2" style="31" width="3.44944451" customWidth="1" outlineLevel="0"/>
+    <col min="3" max="3" style="31" width="5.44944451" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="4" style="31" width="12.11611101" customWidth="1" outlineLevel="0"/>
+    <col min="5" max="5" style="31" width="11.11611101" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="6" style="32" width="10.33833334" customWidth="1" outlineLevel="0"/>
+    <col min="7" max="7" style="31" width="10.44944403" customWidth="1" outlineLevel="0"/>
+    <col min="8" max="8" style="31" width="12.00500033" customWidth="1" outlineLevel="0"/>
+    <col min="9" max="9" style="31" width="13.78277800" customWidth="1" outlineLevel="0"/>
+    <col min="10" max="10" style="1" width="14.78277800" customWidth="1" outlineLevel="0"/>
+    <col min="11" max="11" style="1" width="7.11611101" customWidth="1" outlineLevel="0"/>
+    <col min="12" max="12" style="1" width="13.33833334" customWidth="1" outlineLevel="0"/>
+    <col min="13" max="16384" style="1" width="7.11611101" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="10.5" customHeight="1">
+    <row r="1" spans="1:10" ht="10.500000" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2171,7 +2593,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:10" s="3" customFormat="1" ht="33" customHeight="1">
+    <row r="2" spans="1:10" s="3" customFormat="1" ht="33.000000" customHeight="1">
       <c r="A2" s="88" t="s">
         <v>59</v>
       </c>
@@ -2185,7 +2607,7 @@
       <c r="I2" s="88"/>
       <c r="J2" s="88"/>
     </row>
-    <row r="3" spans="1:10" ht="20" customHeight="1">
+    <row r="3" spans="1:10" ht="20.000000" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -2196,7 +2618,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:10" ht="27" customHeight="1">
+    <row r="4" spans="1:10" ht="27.000000" customHeight="1">
       <c r="A4" s="4"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -2210,7 +2632,7 @@
       <c r="I4" s="95"/>
       <c r="J4" s="95"/>
     </row>
-    <row r="5" spans="1:10" ht="20" customHeight="1">
+    <row r="5" spans="1:10" ht="20.000000" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>46</v>
       </c>
@@ -2226,7 +2648,7 @@
       <c r="I5" s="96"/>
       <c r="J5" s="96"/>
     </row>
-    <row r="6" spans="1:10" ht="23.25" customHeight="1">
+    <row r="6" spans="1:10" ht="23.250000" customHeight="1">
       <c r="A6" s="82" t="s">
         <v>67</v>
       </c>
@@ -2242,7 +2664,7 @@
       <c r="I6" s="92"/>
       <c r="J6" s="92"/>
     </row>
-    <row r="7" spans="1:10" ht="17.25" customHeight="1">
+    <row r="7" spans="1:10" ht="17.250000" customHeight="1">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -2250,13 +2672,13 @@
       <c r="E7" s="12"/>
       <c r="F7" s="7"/>
       <c r="G7" s="92" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="H7" s="92"/>
       <c r="I7" s="92"/>
       <c r="J7" s="92"/>
     </row>
-    <row r="8" spans="1:10" ht="20" customHeight="1">
+    <row r="8" spans="1:10" ht="20.000000" customHeight="1">
       <c r="A8" s="14" t="s">
         <v>0</v>
       </c>
@@ -2272,7 +2694,7 @@
       <c r="I8" s="92"/>
       <c r="J8" s="92"/>
     </row>
-    <row r="9" spans="1:10" s="15" customFormat="1" ht="22" customHeight="1">
+    <row r="9" spans="1:10" s="15" customFormat="1" ht="22.000000" customHeight="1">
       <c r="A9" s="85" t="s">
         <v>71</v>
       </c>
@@ -2288,7 +2710,7 @@
       <c r="I9" s="90"/>
       <c r="J9" s="90"/>
     </row>
-    <row r="10" spans="1:10" ht="17.25" customHeight="1">
+    <row r="10" spans="1:10" ht="17.250000" customHeight="1">
       <c r="A10" s="91"/>
       <c r="B10" s="91"/>
       <c r="C10" s="91"/>
@@ -2304,7 +2726,7 @@
       </c>
       <c r="J10" s="93"/>
     </row>
-    <row r="11" spans="1:10" ht="5.25" customHeight="1">
+    <row r="11" spans="1:10" ht="5.250000" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -2316,7 +2738,7 @@
       <c r="I11" s="97"/>
       <c r="J11" s="97"/>
     </row>
-    <row r="12" spans="1:10" ht="20" customHeight="1">
+    <row r="12" spans="1:10" ht="20.000000" customHeight="1">
       <c r="A12" s="14" t="s">
         <v>1</v>
       </c>
@@ -2330,12 +2752,12 @@
       <c r="I12" s="98"/>
       <c r="J12" s="98"/>
     </row>
-    <row r="13" spans="1:10" ht="20" customHeight="1">
+    <row r="13" spans="1:10" ht="20.000000" customHeight="1">
       <c r="A13" s="9"/>
       <c r="B13" s="19"/>
       <c r="C13" s="20" t="str">
-        <f>IF(K38=0,"일금","일금" &amp; TEXT(K38,"[dbnum4] g/표준"))</f>
-        <v>일금</v>
+        <f>IF(K38=0,"일금","일금"&amp;TEXT(K38,"[dbnum4] g/표준"))</f>
+        <v>일금원정</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="21"/>
@@ -2348,7 +2770,7 @@
       <c r="I13" s="99"/>
       <c r="J13" s="21"/>
     </row>
-    <row r="14" spans="1:10" ht="9.75" customHeight="1" thickBot="1">
+    <row r="14" spans="1:10" ht="9.750000" customHeight="1">
       <c r="A14" s="13"/>
       <c r="B14" s="13"/>
       <c r="C14" s="22"/>
@@ -2360,21 +2782,21 @@
       <c r="I14" s="8"/>
       <c r="J14" s="8"/>
     </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1">
+    <row r="15" spans="1:10" ht="30.000000" customHeight="1">
       <c r="A15" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="101"/>
-      <c r="C15" s="101"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
       <c r="D15" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="101" t="s">
+      <c r="E15" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="101"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="101"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
       <c r="I15" s="23" t="s">
         <v>5</v>
       </c>
@@ -2382,124 +2804,124 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="30" customHeight="1">
-      <c r="A16" s="102"/>
-      <c r="B16" s="103"/>
-      <c r="C16" s="103"/>
+    <row r="16" spans="1:10" ht="30.000000" customHeight="1">
+      <c r="A16" s="101"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
       <c r="D16" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="103" t="s">
+      <c r="E16" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="103"/>
-      <c r="G16" s="103"/>
-      <c r="H16" s="103"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
       <c r="I16" s="26">
         <f>을지!H10</f>
         <v>0</v>
       </c>
       <c r="J16" s="27"/>
     </row>
-    <row r="17" spans="1:12" ht="30" customHeight="1">
-      <c r="A17" s="102"/>
-      <c r="B17" s="103"/>
-      <c r="C17" s="103"/>
+    <row r="17" spans="1:12" ht="30.000000" customHeight="1">
+      <c r="A17" s="101"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
       <c r="D17" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="103" t="s">
+      <c r="E17" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="103"/>
-      <c r="G17" s="103"/>
-      <c r="H17" s="103"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
       <c r="I17" s="26">
         <f>을지!H18</f>
         <v>50000</v>
       </c>
       <c r="J17" s="27"/>
     </row>
-    <row r="18" spans="1:12" ht="30" customHeight="1">
-      <c r="A18" s="102"/>
-      <c r="B18" s="103"/>
-      <c r="C18" s="103"/>
+    <row r="18" spans="1:12" ht="30.000000" customHeight="1">
+      <c r="A18" s="101"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
       <c r="D18" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="103" t="s">
+      <c r="E18" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="103"/>
-      <c r="G18" s="103"/>
-      <c r="H18" s="103"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
       <c r="I18" s="26">
         <f>을지!H19</f>
         <v>0</v>
       </c>
       <c r="J18" s="27"/>
     </row>
-    <row r="19" spans="1:12" ht="30" customHeight="1">
-      <c r="A19" s="102"/>
-      <c r="B19" s="103"/>
-      <c r="C19" s="103"/>
+    <row r="19" spans="1:12" ht="30.000000" customHeight="1">
+      <c r="A19" s="101"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
       <c r="D19" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="103" t="s">
+      <c r="E19" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F19" s="103"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
       <c r="I19" s="26">
         <f>을지!H20</f>
         <v>0</v>
       </c>
       <c r="J19" s="27"/>
     </row>
-    <row r="20" spans="1:12" ht="30" customHeight="1">
-      <c r="A20" s="102"/>
-      <c r="B20" s="103"/>
-      <c r="C20" s="103"/>
+    <row r="20" spans="1:12" ht="30.000000" customHeight="1">
+      <c r="A20" s="101"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
       <c r="D20" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="103" t="s">
+      <c r="E20" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="103"/>
-      <c r="G20" s="103"/>
-      <c r="H20" s="103"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
       <c r="I20" s="26">
         <f>을지!H25</f>
         <v>0</v>
       </c>
       <c r="J20" s="27"/>
     </row>
-    <row r="21" spans="1:12" ht="30" customHeight="1">
-      <c r="A21" s="102"/>
-      <c r="B21" s="103"/>
-      <c r="C21" s="103"/>
+    <row r="21" spans="1:12" ht="30.000000" customHeight="1">
+      <c r="A21" s="101"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
       <c r="D21" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="103" t="s">
+      <c r="E21" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="103"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
       <c r="I21" s="26">
         <f>SUM(I16:I20)</f>
         <v>50000</v>
       </c>
       <c r="J21" s="27"/>
     </row>
-    <row r="22" spans="1:12" ht="30" customHeight="1">
-      <c r="A22" s="102"/>
-      <c r="B22" s="103"/>
-      <c r="C22" s="103"/>
+    <row r="22" spans="1:12" ht="30.000000" customHeight="1">
+      <c r="A22" s="101"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
       <c r="D22" s="25" t="s">
         <v>16</v>
       </c>
@@ -2524,117 +2946,117 @@
       </c>
       <c r="J22" s="27"/>
     </row>
-    <row r="23" spans="1:12" ht="30" customHeight="1">
-      <c r="A23" s="133" t="s">
+    <row r="23" spans="1:12" ht="30.000000" customHeight="1">
+      <c r="A23" s="131" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="134"/>
-      <c r="C23" s="134"/>
-      <c r="D23" s="104" t="s">
+      <c r="B23" s="132"/>
+      <c r="C23" s="132"/>
+      <c r="D23" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="E23" s="105"/>
-      <c r="F23" s="105"/>
-      <c r="G23" s="105"/>
-      <c r="H23" s="105"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="106"/>
-    </row>
-    <row r="24" spans="1:12" ht="30" customHeight="1">
-      <c r="A24" s="113" t="s">
+      <c r="E23" s="103"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="103"/>
+      <c r="J23" s="104"/>
+    </row>
+    <row r="24" spans="1:12" ht="30.000000" customHeight="1">
+      <c r="A24" s="111" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="128"/>
-      <c r="C24" s="129"/>
-      <c r="D24" s="130" t="s">
+      <c r="B24" s="126"/>
+      <c r="C24" s="127"/>
+      <c r="D24" s="128" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="131"/>
-      <c r="F24" s="131"/>
-      <c r="G24" s="131"/>
-      <c r="H24" s="131"/>
-      <c r="I24" s="131"/>
-      <c r="J24" s="132"/>
-    </row>
-    <row r="25" spans="1:12" ht="49.5" customHeight="1">
-      <c r="A25" s="113" t="s">
+      <c r="E24" s="129"/>
+      <c r="F24" s="129"/>
+      <c r="G24" s="129"/>
+      <c r="H24" s="129"/>
+      <c r="I24" s="129"/>
+      <c r="J24" s="130"/>
+    </row>
+    <row r="25" spans="1:12" ht="49.500000" customHeight="1">
+      <c r="A25" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="128"/>
-      <c r="C25" s="129"/>
-      <c r="D25" s="116" t="s">
+      <c r="B25" s="126"/>
+      <c r="C25" s="127"/>
+      <c r="D25" s="114" t="s">
         <v>69</v>
       </c>
-      <c r="E25" s="117"/>
-      <c r="F25" s="117"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="117"/>
-      <c r="I25" s="117"/>
-      <c r="J25" s="118"/>
-    </row>
-    <row r="26" spans="1:12" ht="73.5" customHeight="1">
-      <c r="A26" s="113" t="s">
+      <c r="E25" s="115"/>
+      <c r="F25" s="115"/>
+      <c r="G25" s="115"/>
+      <c r="H25" s="115"/>
+      <c r="I25" s="115"/>
+      <c r="J25" s="116"/>
+    </row>
+    <row r="26" spans="1:12" ht="73.500000" customHeight="1">
+      <c r="A26" s="111" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="114"/>
-      <c r="C26" s="115"/>
-      <c r="D26" s="116" t="s">
+      <c r="B26" s="112"/>
+      <c r="C26" s="113"/>
+      <c r="D26" s="114" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="117"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="117"/>
-      <c r="I26" s="117"/>
-      <c r="J26" s="118"/>
-    </row>
-    <row r="27" spans="1:12" s="28" customFormat="1" ht="30" customHeight="1">
-      <c r="A27" s="119" t="s">
+      <c r="E26" s="115"/>
+      <c r="F26" s="115"/>
+      <c r="G26" s="115"/>
+      <c r="H26" s="115"/>
+      <c r="I26" s="115"/>
+      <c r="J26" s="116"/>
+    </row>
+    <row r="27" spans="1:12" s="28" customFormat="1" ht="30.000000" customHeight="1">
+      <c r="A27" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="120"/>
-      <c r="C27" s="121"/>
-      <c r="D27" s="125" t="s">
+      <c r="B27" s="118"/>
+      <c r="C27" s="119"/>
+      <c r="D27" s="123" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="126"/>
-      <c r="F27" s="127"/>
-      <c r="G27" s="107"/>
-      <c r="H27" s="107"/>
-      <c r="I27" s="107"/>
-      <c r="J27" s="108"/>
-    </row>
-    <row r="28" spans="1:12" s="28" customFormat="1" ht="30" customHeight="1">
-      <c r="A28" s="122"/>
-      <c r="B28" s="123"/>
-      <c r="C28" s="124"/>
-      <c r="D28" s="125"/>
-      <c r="E28" s="126"/>
-      <c r="F28" s="127"/>
-      <c r="G28" s="107"/>
-      <c r="H28" s="107"/>
-      <c r="I28" s="107"/>
-      <c r="J28" s="108"/>
-    </row>
-    <row r="29" spans="1:12" ht="30" customHeight="1" thickBot="1">
-      <c r="A29" s="109" t="s">
+      <c r="E27" s="124"/>
+      <c r="F27" s="125"/>
+      <c r="G27" s="105"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="105"/>
+      <c r="J27" s="106"/>
+    </row>
+    <row r="28" spans="1:12" s="28" customFormat="1" ht="30.000000" customHeight="1">
+      <c r="A28" s="120"/>
+      <c r="B28" s="121"/>
+      <c r="C28" s="122"/>
+      <c r="D28" s="123"/>
+      <c r="E28" s="124"/>
+      <c r="F28" s="125"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="105"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="106"/>
+    </row>
+    <row r="29" spans="1:12" ht="30.000000" customHeight="1">
+      <c r="A29" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="110"/>
-      <c r="C29" s="110"/>
-      <c r="D29" s="111" t="s">
+      <c r="B29" s="108"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="111"/>
-      <c r="F29" s="111"/>
-      <c r="G29" s="111"/>
-      <c r="H29" s="111"/>
-      <c r="I29" s="111"/>
-      <c r="J29" s="112"/>
+      <c r="E29" s="109"/>
+      <c r="F29" s="109"/>
+      <c r="G29" s="109"/>
+      <c r="H29" s="109"/>
+      <c r="I29" s="109"/>
+      <c r="J29" s="110"/>
       <c r="K29" s="29"/>
       <c r="L29" s="29"/>
     </row>
-    <row r="30" spans="1:12" ht="27" customHeight="1">
+    <row r="30" spans="1:12" ht="27.000000" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2844,2732 +3266,2727 @@
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
-    <row r="49" spans="6:6" s="1" customFormat="1">
+    <row r="49" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F49" s="2"/>
     </row>
-    <row r="50" spans="6:6" s="1" customFormat="1">
+    <row r="50" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F50" s="2"/>
     </row>
-    <row r="51" spans="6:6" s="1" customFormat="1">
+    <row r="51" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F51" s="2"/>
     </row>
-    <row r="52" spans="6:6" s="1" customFormat="1">
+    <row r="52" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F52" s="2"/>
     </row>
-    <row r="53" spans="6:6" s="1" customFormat="1">
+    <row r="53" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F53" s="2"/>
     </row>
-    <row r="54" spans="6:6" s="1" customFormat="1">
+    <row r="54" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F54" s="2"/>
     </row>
-    <row r="55" spans="6:6" s="1" customFormat="1">
+    <row r="55" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F55" s="2"/>
     </row>
-    <row r="56" spans="6:6" s="1" customFormat="1">
+    <row r="56" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F56" s="2"/>
     </row>
-    <row r="57" spans="6:6" s="1" customFormat="1">
+    <row r="57" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F57" s="2"/>
     </row>
-    <row r="58" spans="6:6" s="1" customFormat="1">
+    <row r="58" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F58" s="2"/>
     </row>
-    <row r="59" spans="6:6" s="1" customFormat="1">
+    <row r="59" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F59" s="2"/>
     </row>
-    <row r="60" spans="6:6" s="1" customFormat="1">
+    <row r="60" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F60" s="2"/>
     </row>
-    <row r="61" spans="6:6" s="1" customFormat="1">
+    <row r="61" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F61" s="2"/>
     </row>
-    <row r="62" spans="6:6" s="1" customFormat="1">
+    <row r="62" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F62" s="2"/>
     </row>
-    <row r="63" spans="6:6" s="1" customFormat="1">
+    <row r="63" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F63" s="2"/>
     </row>
-    <row r="64" spans="6:6" s="1" customFormat="1">
+    <row r="64" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F64" s="2"/>
     </row>
-    <row r="65" spans="6:6" s="1" customFormat="1">
+    <row r="65" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F65" s="2"/>
     </row>
-    <row r="66" spans="6:6" s="1" customFormat="1">
+    <row r="66" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F66" s="2"/>
     </row>
-    <row r="67" spans="6:6" s="1" customFormat="1">
+    <row r="67" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F67" s="2"/>
     </row>
-    <row r="68" spans="6:6" s="1" customFormat="1">
+    <row r="68" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F68" s="2"/>
     </row>
-    <row r="69" spans="6:6" s="1" customFormat="1">
+    <row r="69" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F69" s="2"/>
     </row>
-    <row r="70" spans="6:6" s="1" customFormat="1">
+    <row r="70" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F70" s="2"/>
     </row>
-    <row r="71" spans="6:6" s="1" customFormat="1">
+    <row r="71" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F71" s="2"/>
     </row>
-    <row r="72" spans="6:6" s="1" customFormat="1">
+    <row r="72" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F72" s="2"/>
     </row>
-    <row r="73" spans="6:6" s="1" customFormat="1">
+    <row r="73" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F73" s="2"/>
     </row>
-    <row r="74" spans="6:6" s="1" customFormat="1">
+    <row r="74" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F74" s="2"/>
     </row>
-    <row r="75" spans="6:6" s="1" customFormat="1">
+    <row r="75" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F75" s="2"/>
     </row>
-    <row r="76" spans="6:6" s="1" customFormat="1">
+    <row r="76" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F76" s="2"/>
     </row>
-    <row r="77" spans="6:6" s="1" customFormat="1">
+    <row r="77" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F77" s="2"/>
     </row>
-    <row r="78" spans="6:6" s="1" customFormat="1">
+    <row r="78" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F78" s="2"/>
     </row>
-    <row r="79" spans="6:6" s="1" customFormat="1">
+    <row r="79" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F79" s="2"/>
     </row>
-    <row r="80" spans="6:6" s="1" customFormat="1">
+    <row r="80" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F80" s="2"/>
     </row>
-    <row r="81" spans="6:6" s="1" customFormat="1">
+    <row r="81" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F81" s="2"/>
     </row>
-    <row r="82" spans="6:6" s="1" customFormat="1">
+    <row r="82" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F82" s="2"/>
     </row>
-    <row r="83" spans="6:6" s="1" customFormat="1">
+    <row r="83" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F83" s="2"/>
     </row>
-    <row r="84" spans="6:6" s="1" customFormat="1">
+    <row r="84" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F84" s="2"/>
     </row>
-    <row r="85" spans="6:6" s="1" customFormat="1">
+    <row r="85" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F85" s="2"/>
     </row>
-    <row r="86" spans="6:6" s="1" customFormat="1">
+    <row r="86" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F86" s="2"/>
     </row>
-    <row r="87" spans="6:6" s="1" customFormat="1">
+    <row r="87" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F87" s="2"/>
     </row>
-    <row r="88" spans="6:6" s="1" customFormat="1">
+    <row r="88" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F88" s="2"/>
     </row>
-    <row r="89" spans="6:6" s="1" customFormat="1">
+    <row r="89" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F89" s="2"/>
     </row>
-    <row r="90" spans="6:6" s="1" customFormat="1">
+    <row r="90" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F90" s="2"/>
     </row>
-    <row r="91" spans="6:6" s="1" customFormat="1">
+    <row r="91" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F91" s="2"/>
     </row>
-    <row r="92" spans="6:6" s="1" customFormat="1">
+    <row r="92" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F92" s="2"/>
     </row>
-    <row r="93" spans="6:6" s="1" customFormat="1">
+    <row r="93" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F93" s="2"/>
     </row>
-    <row r="94" spans="6:6" s="1" customFormat="1">
+    <row r="94" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F94" s="2"/>
     </row>
-    <row r="95" spans="6:6" s="1" customFormat="1">
+    <row r="95" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F95" s="2"/>
     </row>
-    <row r="96" spans="6:6" s="1" customFormat="1">
+    <row r="96" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F96" s="2"/>
     </row>
-    <row r="97" spans="6:6" s="1" customFormat="1">
+    <row r="97" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F97" s="2"/>
     </row>
-    <row r="98" spans="6:6" s="1" customFormat="1">
+    <row r="98" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F98" s="2"/>
     </row>
-    <row r="99" spans="6:6" s="1" customFormat="1">
+    <row r="99" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F99" s="2"/>
     </row>
-    <row r="100" spans="6:6" s="1" customFormat="1">
+    <row r="100" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F100" s="2"/>
     </row>
-    <row r="101" spans="6:6" s="1" customFormat="1">
+    <row r="101" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F101" s="2"/>
     </row>
-    <row r="102" spans="6:6" s="1" customFormat="1">
+    <row r="102" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F102" s="2"/>
     </row>
-    <row r="103" spans="6:6" s="1" customFormat="1">
+    <row r="103" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F103" s="2"/>
     </row>
-    <row r="104" spans="6:6" s="1" customFormat="1">
+    <row r="104" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F104" s="2"/>
     </row>
-    <row r="105" spans="6:6" s="1" customFormat="1">
+    <row r="105" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F105" s="2"/>
     </row>
-    <row r="106" spans="6:6" s="1" customFormat="1">
+    <row r="106" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F106" s="2"/>
     </row>
-    <row r="107" spans="6:6" s="1" customFormat="1">
+    <row r="107" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F107" s="2"/>
     </row>
-    <row r="108" spans="6:6" s="1" customFormat="1">
+    <row r="108" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F108" s="2"/>
     </row>
-    <row r="109" spans="6:6" s="1" customFormat="1">
+    <row r="109" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F109" s="2"/>
     </row>
-    <row r="110" spans="6:6" s="1" customFormat="1">
+    <row r="110" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F110" s="2"/>
     </row>
-    <row r="111" spans="6:6" s="1" customFormat="1">
+    <row r="111" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F111" s="2"/>
     </row>
-    <row r="112" spans="6:6" s="1" customFormat="1">
+    <row r="112" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F112" s="2"/>
     </row>
-    <row r="113" spans="6:6" s="1" customFormat="1">
+    <row r="113" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F113" s="2"/>
     </row>
-    <row r="114" spans="6:6" s="1" customFormat="1">
+    <row r="114" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F114" s="2"/>
     </row>
-    <row r="115" spans="6:6" s="1" customFormat="1">
+    <row r="115" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F115" s="2"/>
     </row>
-    <row r="116" spans="6:6" s="1" customFormat="1">
+    <row r="116" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F116" s="2"/>
     </row>
-    <row r="117" spans="6:6" s="1" customFormat="1">
+    <row r="117" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F117" s="2"/>
     </row>
-    <row r="118" spans="6:6" s="1" customFormat="1">
+    <row r="118" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F118" s="2"/>
     </row>
-    <row r="119" spans="6:6" s="1" customFormat="1">
+    <row r="119" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F119" s="2"/>
     </row>
-    <row r="120" spans="6:6" s="1" customFormat="1">
+    <row r="120" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F120" s="2"/>
     </row>
-    <row r="121" spans="6:6" s="1" customFormat="1">
+    <row r="121" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F121" s="2"/>
     </row>
-    <row r="122" spans="6:6" s="1" customFormat="1">
+    <row r="122" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F122" s="2"/>
     </row>
-    <row r="123" spans="6:6" s="1" customFormat="1">
+    <row r="123" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F123" s="2"/>
     </row>
-    <row r="124" spans="6:6" s="1" customFormat="1">
+    <row r="124" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F124" s="2"/>
     </row>
-    <row r="125" spans="6:6" s="1" customFormat="1">
+    <row r="125" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F125" s="2"/>
     </row>
-    <row r="126" spans="6:6" s="1" customFormat="1">
+    <row r="126" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F126" s="2"/>
     </row>
-    <row r="127" spans="6:6" s="1" customFormat="1">
+    <row r="127" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F127" s="2"/>
     </row>
-    <row r="128" spans="6:6" s="1" customFormat="1">
+    <row r="128" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F128" s="2"/>
     </row>
-    <row r="129" spans="6:6" s="1" customFormat="1">
+    <row r="129" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F129" s="2"/>
     </row>
-    <row r="130" spans="6:6" s="1" customFormat="1">
+    <row r="130" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F130" s="2"/>
     </row>
-    <row r="131" spans="6:6" s="1" customFormat="1">
+    <row r="131" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F131" s="2"/>
     </row>
-    <row r="132" spans="6:6" s="1" customFormat="1">
+    <row r="132" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F132" s="2"/>
     </row>
-    <row r="133" spans="6:6" s="1" customFormat="1">
+    <row r="133" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F133" s="2"/>
     </row>
-    <row r="134" spans="6:6" s="1" customFormat="1">
+    <row r="134" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F134" s="2"/>
     </row>
-    <row r="135" spans="6:6" s="1" customFormat="1">
+    <row r="135" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F135" s="2"/>
     </row>
-    <row r="136" spans="6:6" s="1" customFormat="1">
+    <row r="136" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F136" s="2"/>
     </row>
-    <row r="137" spans="6:6" s="1" customFormat="1">
+    <row r="137" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F137" s="2"/>
     </row>
-    <row r="138" spans="6:6" s="1" customFormat="1">
+    <row r="138" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F138" s="2"/>
     </row>
-    <row r="139" spans="6:6" s="1" customFormat="1">
+    <row r="139" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F139" s="2"/>
     </row>
-    <row r="140" spans="6:6" s="1" customFormat="1">
+    <row r="140" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F140" s="2"/>
     </row>
-    <row r="141" spans="6:6" s="1" customFormat="1">
+    <row r="141" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F141" s="2"/>
     </row>
-    <row r="142" spans="6:6" s="1" customFormat="1">
+    <row r="142" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F142" s="2"/>
     </row>
-    <row r="143" spans="6:6" s="1" customFormat="1">
+    <row r="143" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F143" s="2"/>
     </row>
-    <row r="144" spans="6:6" s="1" customFormat="1">
+    <row r="144" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F144" s="2"/>
     </row>
-    <row r="145" spans="6:6" s="1" customFormat="1">
+    <row r="145" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F145" s="2"/>
     </row>
-    <row r="146" spans="6:6" s="1" customFormat="1">
+    <row r="146" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F146" s="2"/>
     </row>
-    <row r="147" spans="6:6" s="1" customFormat="1">
+    <row r="147" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F147" s="2"/>
     </row>
-    <row r="148" spans="6:6" s="1" customFormat="1">
+    <row r="148" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F148" s="2"/>
     </row>
-    <row r="149" spans="6:6" s="1" customFormat="1">
+    <row r="149" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F149" s="2"/>
     </row>
-    <row r="150" spans="6:6" s="1" customFormat="1">
+    <row r="150" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F150" s="2"/>
     </row>
-    <row r="151" spans="6:6" s="1" customFormat="1">
+    <row r="151" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F151" s="2"/>
     </row>
-    <row r="152" spans="6:6" s="1" customFormat="1">
+    <row r="152" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F152" s="2"/>
     </row>
-    <row r="153" spans="6:6" s="1" customFormat="1">
+    <row r="153" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F153" s="2"/>
     </row>
-    <row r="154" spans="6:6" s="1" customFormat="1">
+    <row r="154" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F154" s="2"/>
     </row>
-    <row r="155" spans="6:6" s="1" customFormat="1">
+    <row r="155" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F155" s="2"/>
     </row>
-    <row r="156" spans="6:6" s="1" customFormat="1">
+    <row r="156" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F156" s="2"/>
     </row>
-    <row r="157" spans="6:6" s="1" customFormat="1">
+    <row r="157" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F157" s="2"/>
     </row>
-    <row r="158" spans="6:6" s="1" customFormat="1">
+    <row r="158" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F158" s="2"/>
     </row>
-    <row r="159" spans="6:6" s="1" customFormat="1">
+    <row r="159" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F159" s="2"/>
     </row>
-    <row r="160" spans="6:6" s="1" customFormat="1">
+    <row r="160" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F160" s="2"/>
     </row>
-    <row r="161" spans="6:6" s="1" customFormat="1">
+    <row r="161" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F161" s="2"/>
     </row>
-    <row r="162" spans="6:6" s="1" customFormat="1">
+    <row r="162" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F162" s="2"/>
     </row>
-    <row r="163" spans="6:6" s="1" customFormat="1">
+    <row r="163" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F163" s="2"/>
     </row>
-    <row r="164" spans="6:6" s="1" customFormat="1">
+    <row r="164" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F164" s="2"/>
     </row>
-    <row r="165" spans="6:6" s="1" customFormat="1">
+    <row r="165" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F165" s="2"/>
     </row>
-    <row r="166" spans="6:6" s="1" customFormat="1">
+    <row r="166" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F166" s="2"/>
     </row>
-    <row r="167" spans="6:6" s="1" customFormat="1">
+    <row r="167" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F167" s="2"/>
     </row>
-    <row r="168" spans="6:6" s="1" customFormat="1">
+    <row r="168" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F168" s="2"/>
     </row>
-    <row r="169" spans="6:6" s="1" customFormat="1">
+    <row r="169" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F169" s="2"/>
     </row>
-    <row r="170" spans="6:6" s="1" customFormat="1">
+    <row r="170" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F170" s="2"/>
     </row>
-    <row r="171" spans="6:6" s="1" customFormat="1">
+    <row r="171" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F171" s="2"/>
     </row>
-    <row r="172" spans="6:6" s="1" customFormat="1">
+    <row r="172" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F172" s="2"/>
     </row>
-    <row r="173" spans="6:6" s="1" customFormat="1">
+    <row r="173" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F173" s="2"/>
     </row>
-    <row r="174" spans="6:6" s="1" customFormat="1">
+    <row r="174" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F174" s="2"/>
     </row>
-    <row r="175" spans="6:6" s="1" customFormat="1">
+    <row r="175" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F175" s="2"/>
     </row>
-    <row r="176" spans="6:6" s="1" customFormat="1">
+    <row r="176" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F176" s="2"/>
     </row>
-    <row r="177" spans="6:6" s="1" customFormat="1">
+    <row r="177" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F177" s="2"/>
     </row>
-    <row r="178" spans="6:6" s="1" customFormat="1">
+    <row r="178" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F178" s="2"/>
     </row>
-    <row r="179" spans="6:6" s="1" customFormat="1">
+    <row r="179" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F179" s="2"/>
     </row>
-    <row r="180" spans="6:6" s="1" customFormat="1">
+    <row r="180" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F180" s="2"/>
     </row>
-    <row r="181" spans="6:6" s="1" customFormat="1">
+    <row r="181" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F181" s="2"/>
     </row>
-    <row r="182" spans="6:6" s="1" customFormat="1">
+    <row r="182" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F182" s="2"/>
     </row>
-    <row r="183" spans="6:6" s="1" customFormat="1">
+    <row r="183" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F183" s="2"/>
     </row>
-    <row r="184" spans="6:6" s="1" customFormat="1">
+    <row r="184" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F184" s="2"/>
     </row>
-    <row r="185" spans="6:6" s="1" customFormat="1">
+    <row r="185" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F185" s="2"/>
     </row>
-    <row r="186" spans="6:6" s="1" customFormat="1">
+    <row r="186" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F186" s="2"/>
     </row>
-    <row r="187" spans="6:6" s="1" customFormat="1">
+    <row r="187" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F187" s="2"/>
     </row>
-    <row r="188" spans="6:6" s="1" customFormat="1">
+    <row r="188" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F188" s="2"/>
     </row>
-    <row r="189" spans="6:6" s="1" customFormat="1">
+    <row r="189" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F189" s="2"/>
     </row>
-    <row r="190" spans="6:6" s="1" customFormat="1">
+    <row r="190" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F190" s="2"/>
     </row>
-    <row r="191" spans="6:6" s="1" customFormat="1">
+    <row r="191" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F191" s="2"/>
     </row>
-    <row r="192" spans="6:6" s="1" customFormat="1">
+    <row r="192" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F192" s="2"/>
     </row>
-    <row r="193" spans="6:6" s="1" customFormat="1">
+    <row r="193" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F193" s="2"/>
     </row>
-    <row r="194" spans="6:6" s="1" customFormat="1">
+    <row r="194" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F194" s="2"/>
     </row>
-    <row r="195" spans="6:6" s="1" customFormat="1">
+    <row r="195" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F195" s="2"/>
     </row>
-    <row r="196" spans="6:6" s="1" customFormat="1">
+    <row r="196" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F196" s="2"/>
     </row>
-    <row r="197" spans="6:6" s="1" customFormat="1">
+    <row r="197" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F197" s="2"/>
     </row>
-    <row r="198" spans="6:6" s="1" customFormat="1">
+    <row r="198" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F198" s="2"/>
     </row>
-    <row r="199" spans="6:6" s="1" customFormat="1">
+    <row r="199" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F199" s="2"/>
     </row>
-    <row r="200" spans="6:6" s="1" customFormat="1">
+    <row r="200" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F200" s="2"/>
     </row>
-    <row r="201" spans="6:6" s="1" customFormat="1">
+    <row r="201" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F201" s="2"/>
     </row>
-    <row r="202" spans="6:6" s="1" customFormat="1">
+    <row r="202" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F202" s="2"/>
     </row>
-    <row r="203" spans="6:6" s="1" customFormat="1">
+    <row r="203" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F203" s="2"/>
     </row>
-    <row r="204" spans="6:6" s="1" customFormat="1">
+    <row r="204" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F204" s="2"/>
     </row>
-    <row r="205" spans="6:6" s="1" customFormat="1">
+    <row r="205" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F205" s="2"/>
     </row>
-    <row r="206" spans="6:6" s="1" customFormat="1">
+    <row r="206" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F206" s="2"/>
     </row>
-    <row r="207" spans="6:6" s="1" customFormat="1">
+    <row r="207" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F207" s="2"/>
     </row>
-    <row r="208" spans="6:6" s="1" customFormat="1">
+    <row r="208" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F208" s="2"/>
     </row>
-    <row r="209" spans="6:6" s="1" customFormat="1">
+    <row r="209" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F209" s="2"/>
     </row>
-    <row r="210" spans="6:6" s="1" customFormat="1">
+    <row r="210" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F210" s="2"/>
     </row>
-    <row r="211" spans="6:6" s="1" customFormat="1">
+    <row r="211" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F211" s="2"/>
     </row>
-    <row r="212" spans="6:6" s="1" customFormat="1">
+    <row r="212" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F212" s="2"/>
     </row>
-    <row r="213" spans="6:6" s="1" customFormat="1">
+    <row r="213" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F213" s="2"/>
     </row>
-    <row r="214" spans="6:6" s="1" customFormat="1">
+    <row r="214" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F214" s="2"/>
     </row>
-    <row r="215" spans="6:6" s="1" customFormat="1">
+    <row r="215" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F215" s="2"/>
     </row>
-    <row r="216" spans="6:6" s="1" customFormat="1">
+    <row r="216" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F216" s="2"/>
     </row>
-    <row r="217" spans="6:6" s="1" customFormat="1">
+    <row r="217" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F217" s="2"/>
     </row>
-    <row r="218" spans="6:6" s="1" customFormat="1">
+    <row r="218" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F218" s="2"/>
     </row>
-    <row r="219" spans="6:6" s="1" customFormat="1">
+    <row r="219" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F219" s="2"/>
     </row>
-    <row r="220" spans="6:6" s="1" customFormat="1">
+    <row r="220" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F220" s="2"/>
     </row>
-    <row r="221" spans="6:6" s="1" customFormat="1">
+    <row r="221" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F221" s="2"/>
     </row>
-    <row r="222" spans="6:6" s="1" customFormat="1">
+    <row r="222" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F222" s="2"/>
     </row>
-    <row r="223" spans="6:6" s="1" customFormat="1">
+    <row r="223" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F223" s="2"/>
     </row>
-    <row r="224" spans="6:6" s="1" customFormat="1">
+    <row r="224" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F224" s="2"/>
     </row>
-    <row r="225" spans="6:6" s="1" customFormat="1">
+    <row r="225" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F225" s="2"/>
     </row>
-    <row r="226" spans="6:6" s="1" customFormat="1">
+    <row r="226" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F226" s="2"/>
     </row>
-    <row r="227" spans="6:6" s="1" customFormat="1">
+    <row r="227" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F227" s="2"/>
     </row>
-    <row r="228" spans="6:6" s="1" customFormat="1">
+    <row r="228" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F228" s="2"/>
     </row>
-    <row r="229" spans="6:6" s="1" customFormat="1">
+    <row r="229" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F229" s="2"/>
     </row>
-    <row r="230" spans="6:6" s="1" customFormat="1">
+    <row r="230" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F230" s="2"/>
     </row>
-    <row r="231" spans="6:6" s="1" customFormat="1">
+    <row r="231" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F231" s="2"/>
     </row>
-    <row r="232" spans="6:6" s="1" customFormat="1">
+    <row r="232" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F232" s="2"/>
     </row>
-    <row r="233" spans="6:6" s="1" customFormat="1">
+    <row r="233" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F233" s="2"/>
     </row>
-    <row r="234" spans="6:6" s="1" customFormat="1">
+    <row r="234" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F234" s="2"/>
     </row>
-    <row r="235" spans="6:6" s="1" customFormat="1">
+    <row r="235" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F235" s="2"/>
     </row>
-    <row r="236" spans="6:6" s="1" customFormat="1">
+    <row r="236" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F236" s="2"/>
     </row>
-    <row r="237" spans="6:6" s="1" customFormat="1">
+    <row r="237" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F237" s="2"/>
     </row>
-    <row r="238" spans="6:6" s="1" customFormat="1">
+    <row r="238" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F238" s="2"/>
     </row>
-    <row r="239" spans="6:6" s="1" customFormat="1">
+    <row r="239" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F239" s="2"/>
     </row>
-    <row r="240" spans="6:6" s="1" customFormat="1">
+    <row r="240" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F240" s="2"/>
     </row>
-    <row r="241" spans="6:6" s="1" customFormat="1">
+    <row r="241" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F241" s="2"/>
     </row>
-    <row r="242" spans="6:6" s="1" customFormat="1">
+    <row r="242" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F242" s="2"/>
     </row>
-    <row r="243" spans="6:6" s="1" customFormat="1">
+    <row r="243" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F243" s="2"/>
     </row>
-    <row r="244" spans="6:6" s="1" customFormat="1">
+    <row r="244" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F244" s="2"/>
     </row>
-    <row r="245" spans="6:6" s="1" customFormat="1">
+    <row r="245" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F245" s="2"/>
     </row>
-    <row r="246" spans="6:6" s="1" customFormat="1">
+    <row r="246" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F246" s="2"/>
     </row>
-    <row r="247" spans="6:6" s="1" customFormat="1">
+    <row r="247" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F247" s="2"/>
     </row>
-    <row r="248" spans="6:6" s="1" customFormat="1">
+    <row r="248" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F248" s="2"/>
     </row>
-    <row r="249" spans="6:6" s="1" customFormat="1">
+    <row r="249" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F249" s="2"/>
     </row>
-    <row r="250" spans="6:6" s="1" customFormat="1">
+    <row r="250" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F250" s="2"/>
     </row>
-    <row r="251" spans="6:6" s="1" customFormat="1">
+    <row r="251" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F251" s="2"/>
     </row>
-    <row r="252" spans="6:6" s="1" customFormat="1">
+    <row r="252" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F252" s="2"/>
     </row>
-    <row r="253" spans="6:6" s="1" customFormat="1">
+    <row r="253" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F253" s="2"/>
     </row>
-    <row r="254" spans="6:6" s="1" customFormat="1">
+    <row r="254" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F254" s="2"/>
     </row>
-    <row r="255" spans="6:6" s="1" customFormat="1">
+    <row r="255" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F255" s="2"/>
     </row>
-    <row r="256" spans="6:6" s="1" customFormat="1">
+    <row r="256" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F256" s="2"/>
     </row>
-    <row r="257" spans="6:6" s="1" customFormat="1">
+    <row r="257" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F257" s="2"/>
     </row>
-    <row r="258" spans="6:6" s="1" customFormat="1">
+    <row r="258" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F258" s="2"/>
     </row>
-    <row r="259" spans="6:6" s="1" customFormat="1">
+    <row r="259" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F259" s="2"/>
     </row>
-    <row r="260" spans="6:6" s="1" customFormat="1">
+    <row r="260" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F260" s="2"/>
     </row>
-    <row r="261" spans="6:6" s="1" customFormat="1">
+    <row r="261" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F261" s="2"/>
     </row>
-    <row r="262" spans="6:6" s="1" customFormat="1">
+    <row r="262" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F262" s="2"/>
     </row>
-    <row r="263" spans="6:6" s="1" customFormat="1">
+    <row r="263" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F263" s="2"/>
     </row>
-    <row r="264" spans="6:6" s="1" customFormat="1">
+    <row r="264" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F264" s="2"/>
     </row>
-    <row r="265" spans="6:6" s="1" customFormat="1">
+    <row r="265" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F265" s="2"/>
     </row>
-    <row r="266" spans="6:6" s="1" customFormat="1">
+    <row r="266" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F266" s="2"/>
     </row>
-    <row r="267" spans="6:6" s="1" customFormat="1">
+    <row r="267" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F267" s="2"/>
     </row>
-    <row r="268" spans="6:6" s="1" customFormat="1">
+    <row r="268" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F268" s="2"/>
     </row>
-    <row r="269" spans="6:6" s="1" customFormat="1">
+    <row r="269" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F269" s="2"/>
     </row>
-    <row r="270" spans="6:6" s="1" customFormat="1">
+    <row r="270" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F270" s="2"/>
     </row>
-    <row r="271" spans="6:6" s="1" customFormat="1">
+    <row r="271" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F271" s="2"/>
     </row>
-    <row r="272" spans="6:6" s="1" customFormat="1">
+    <row r="272" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F272" s="2"/>
     </row>
-    <row r="273" spans="6:6" s="1" customFormat="1">
+    <row r="273" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F273" s="2"/>
     </row>
-    <row r="274" spans="6:6" s="1" customFormat="1">
+    <row r="274" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F274" s="2"/>
     </row>
-    <row r="275" spans="6:6" s="1" customFormat="1">
+    <row r="275" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F275" s="2"/>
     </row>
-    <row r="276" spans="6:6" s="1" customFormat="1">
+    <row r="276" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F276" s="2"/>
     </row>
-    <row r="277" spans="6:6" s="1" customFormat="1">
+    <row r="277" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F277" s="2"/>
     </row>
-    <row r="278" spans="6:6" s="1" customFormat="1">
+    <row r="278" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F278" s="2"/>
     </row>
-    <row r="279" spans="6:6" s="1" customFormat="1">
+    <row r="279" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F279" s="2"/>
     </row>
-    <row r="280" spans="6:6" s="1" customFormat="1">
+    <row r="280" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F280" s="2"/>
     </row>
-    <row r="281" spans="6:6" s="1" customFormat="1">
+    <row r="281" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F281" s="2"/>
     </row>
-    <row r="282" spans="6:6" s="1" customFormat="1">
+    <row r="282" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F282" s="2"/>
     </row>
-    <row r="283" spans="6:6" s="1" customFormat="1">
+    <row r="283" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F283" s="2"/>
     </row>
-    <row r="284" spans="6:6" s="1" customFormat="1">
+    <row r="284" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F284" s="2"/>
     </row>
-    <row r="285" spans="6:6" s="1" customFormat="1">
+    <row r="285" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F285" s="2"/>
     </row>
-    <row r="286" spans="6:6" s="1" customFormat="1">
+    <row r="286" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F286" s="2"/>
     </row>
-    <row r="287" spans="6:6" s="1" customFormat="1">
+    <row r="287" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F287" s="2"/>
     </row>
-    <row r="288" spans="6:6" s="1" customFormat="1">
+    <row r="288" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F288" s="2"/>
     </row>
-    <row r="289" spans="6:6" s="1" customFormat="1">
+    <row r="289" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F289" s="2"/>
     </row>
-    <row r="290" spans="6:6" s="1" customFormat="1">
+    <row r="290" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F290" s="2"/>
     </row>
-    <row r="291" spans="6:6" s="1" customFormat="1">
+    <row r="291" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F291" s="2"/>
     </row>
-    <row r="292" spans="6:6" s="1" customFormat="1">
+    <row r="292" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F292" s="2"/>
     </row>
-    <row r="293" spans="6:6" s="1" customFormat="1">
+    <row r="293" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F293" s="2"/>
     </row>
-    <row r="294" spans="6:6" s="1" customFormat="1">
+    <row r="294" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F294" s="2"/>
     </row>
-    <row r="295" spans="6:6" s="1" customFormat="1">
+    <row r="295" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F295" s="2"/>
     </row>
-    <row r="296" spans="6:6" s="1" customFormat="1">
+    <row r="296" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F296" s="2"/>
     </row>
-    <row r="297" spans="6:6" s="1" customFormat="1">
+    <row r="297" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F297" s="2"/>
     </row>
-    <row r="298" spans="6:6" s="1" customFormat="1">
+    <row r="298" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F298" s="2"/>
     </row>
-    <row r="299" spans="6:6" s="1" customFormat="1">
+    <row r="299" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F299" s="2"/>
     </row>
-    <row r="300" spans="6:6" s="1" customFormat="1">
+    <row r="300" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F300" s="2"/>
     </row>
-    <row r="301" spans="6:6" s="1" customFormat="1">
+    <row r="301" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F301" s="2"/>
     </row>
-    <row r="302" spans="6:6" s="1" customFormat="1">
+    <row r="302" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F302" s="2"/>
     </row>
-    <row r="303" spans="6:6" s="1" customFormat="1">
+    <row r="303" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F303" s="2"/>
     </row>
-    <row r="304" spans="6:6" s="1" customFormat="1">
+    <row r="304" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F304" s="2"/>
     </row>
-    <row r="305" spans="6:6" s="1" customFormat="1">
+    <row r="305" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F305" s="2"/>
     </row>
-    <row r="306" spans="6:6" s="1" customFormat="1">
+    <row r="306" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F306" s="2"/>
     </row>
-    <row r="307" spans="6:6" s="1" customFormat="1">
+    <row r="307" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F307" s="2"/>
     </row>
-    <row r="308" spans="6:6" s="1" customFormat="1">
+    <row r="308" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F308" s="2"/>
     </row>
-    <row r="309" spans="6:6" s="1" customFormat="1">
+    <row r="309" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F309" s="2"/>
     </row>
-    <row r="310" spans="6:6" s="1" customFormat="1">
+    <row r="310" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F310" s="2"/>
     </row>
-    <row r="311" spans="6:6" s="1" customFormat="1">
+    <row r="311" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F311" s="2"/>
     </row>
-    <row r="312" spans="6:6" s="1" customFormat="1">
+    <row r="312" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F312" s="2"/>
     </row>
-    <row r="313" spans="6:6" s="1" customFormat="1">
+    <row r="313" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F313" s="2"/>
     </row>
-    <row r="314" spans="6:6" s="1" customFormat="1">
+    <row r="314" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F314" s="2"/>
     </row>
-    <row r="315" spans="6:6" s="1" customFormat="1">
+    <row r="315" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F315" s="2"/>
     </row>
-    <row r="316" spans="6:6" s="1" customFormat="1">
+    <row r="316" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F316" s="2"/>
     </row>
-    <row r="317" spans="6:6" s="1" customFormat="1">
+    <row r="317" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F317" s="2"/>
     </row>
-    <row r="318" spans="6:6" s="1" customFormat="1">
+    <row r="318" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F318" s="2"/>
     </row>
-    <row r="319" spans="6:6" s="1" customFormat="1">
+    <row r="319" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F319" s="2"/>
     </row>
-    <row r="320" spans="6:6" s="1" customFormat="1">
+    <row r="320" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F320" s="2"/>
     </row>
-    <row r="321" spans="6:6" s="1" customFormat="1">
+    <row r="321" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F321" s="2"/>
     </row>
-    <row r="322" spans="6:6" s="1" customFormat="1">
+    <row r="322" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F322" s="2"/>
     </row>
-    <row r="323" spans="6:6" s="1" customFormat="1">
+    <row r="323" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F323" s="2"/>
     </row>
-    <row r="324" spans="6:6" s="1" customFormat="1">
+    <row r="324" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F324" s="2"/>
     </row>
-    <row r="325" spans="6:6" s="1" customFormat="1">
+    <row r="325" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F325" s="2"/>
     </row>
-    <row r="326" spans="6:6" s="1" customFormat="1">
+    <row r="326" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F326" s="2"/>
     </row>
-    <row r="327" spans="6:6" s="1" customFormat="1">
+    <row r="327" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F327" s="2"/>
     </row>
-    <row r="328" spans="6:6" s="1" customFormat="1">
+    <row r="328" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F328" s="2"/>
     </row>
-    <row r="329" spans="6:6" s="1" customFormat="1">
+    <row r="329" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F329" s="2"/>
     </row>
-    <row r="330" spans="6:6" s="1" customFormat="1">
+    <row r="330" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F330" s="2"/>
     </row>
-    <row r="331" spans="6:6" s="1" customFormat="1">
+    <row r="331" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F331" s="2"/>
     </row>
-    <row r="332" spans="6:6" s="1" customFormat="1">
+    <row r="332" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F332" s="2"/>
     </row>
-    <row r="333" spans="6:6" s="1" customFormat="1">
+    <row r="333" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F333" s="2"/>
     </row>
-    <row r="334" spans="6:6" s="1" customFormat="1">
+    <row r="334" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F334" s="2"/>
     </row>
-    <row r="335" spans="6:6" s="1" customFormat="1">
+    <row r="335" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F335" s="2"/>
     </row>
-    <row r="336" spans="6:6" s="1" customFormat="1">
+    <row r="336" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F336" s="2"/>
     </row>
-    <row r="337" spans="6:6" s="1" customFormat="1">
+    <row r="337" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F337" s="2"/>
     </row>
-    <row r="338" spans="6:6" s="1" customFormat="1">
+    <row r="338" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F338" s="2"/>
     </row>
-    <row r="339" spans="6:6" s="1" customFormat="1">
+    <row r="339" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F339" s="2"/>
     </row>
-    <row r="340" spans="6:6" s="1" customFormat="1">
+    <row r="340" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F340" s="2"/>
     </row>
-    <row r="341" spans="6:6" s="1" customFormat="1">
+    <row r="341" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F341" s="2"/>
     </row>
-    <row r="342" spans="6:6" s="1" customFormat="1">
+    <row r="342" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F342" s="2"/>
     </row>
-    <row r="343" spans="6:6" s="1" customFormat="1">
+    <row r="343" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F343" s="2"/>
     </row>
-    <row r="344" spans="6:6" s="1" customFormat="1">
+    <row r="344" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F344" s="2"/>
     </row>
-    <row r="345" spans="6:6" s="1" customFormat="1">
+    <row r="345" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F345" s="2"/>
     </row>
-    <row r="346" spans="6:6" s="1" customFormat="1">
+    <row r="346" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F346" s="2"/>
     </row>
-    <row r="347" spans="6:6" s="1" customFormat="1">
+    <row r="347" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F347" s="2"/>
     </row>
-    <row r="348" spans="6:6" s="1" customFormat="1">
+    <row r="348" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F348" s="2"/>
     </row>
-    <row r="349" spans="6:6" s="1" customFormat="1">
+    <row r="349" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F349" s="2"/>
     </row>
-    <row r="350" spans="6:6" s="1" customFormat="1">
+    <row r="350" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F350" s="2"/>
     </row>
-    <row r="351" spans="6:6" s="1" customFormat="1">
+    <row r="351" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F351" s="2"/>
     </row>
-    <row r="352" spans="6:6" s="1" customFormat="1">
+    <row r="352" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F352" s="2"/>
     </row>
-    <row r="353" spans="6:6" s="1" customFormat="1">
+    <row r="353" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F353" s="2"/>
     </row>
-    <row r="354" spans="6:6" s="1" customFormat="1">
+    <row r="354" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F354" s="2"/>
     </row>
-    <row r="355" spans="6:6" s="1" customFormat="1">
+    <row r="355" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F355" s="2"/>
     </row>
-    <row r="356" spans="6:6" s="1" customFormat="1">
+    <row r="356" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F356" s="2"/>
     </row>
-    <row r="357" spans="6:6" s="1" customFormat="1">
+    <row r="357" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F357" s="2"/>
     </row>
-    <row r="358" spans="6:6" s="1" customFormat="1">
+    <row r="358" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F358" s="2"/>
     </row>
-    <row r="359" spans="6:6" s="1" customFormat="1">
+    <row r="359" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F359" s="2"/>
     </row>
-    <row r="360" spans="6:6" s="1" customFormat="1">
+    <row r="360" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F360" s="2"/>
     </row>
-    <row r="361" spans="6:6" s="1" customFormat="1">
+    <row r="361" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F361" s="2"/>
     </row>
-    <row r="362" spans="6:6" s="1" customFormat="1">
+    <row r="362" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F362" s="2"/>
     </row>
-    <row r="363" spans="6:6" s="1" customFormat="1">
+    <row r="363" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F363" s="2"/>
     </row>
-    <row r="364" spans="6:6" s="1" customFormat="1">
+    <row r="364" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F364" s="2"/>
     </row>
-    <row r="365" spans="6:6" s="1" customFormat="1">
+    <row r="365" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F365" s="2"/>
     </row>
-    <row r="366" spans="6:6" s="1" customFormat="1">
+    <row r="366" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F366" s="2"/>
     </row>
-    <row r="367" spans="6:6" s="1" customFormat="1">
+    <row r="367" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F367" s="2"/>
     </row>
-    <row r="368" spans="6:6" s="1" customFormat="1">
+    <row r="368" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F368" s="2"/>
     </row>
-    <row r="369" spans="6:6" s="1" customFormat="1">
+    <row r="369" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F369" s="2"/>
     </row>
-    <row r="370" spans="6:6" s="1" customFormat="1">
+    <row r="370" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F370" s="2"/>
     </row>
-    <row r="371" spans="6:6" s="1" customFormat="1">
+    <row r="371" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F371" s="2"/>
     </row>
-    <row r="372" spans="6:6" s="1" customFormat="1">
+    <row r="372" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F372" s="2"/>
     </row>
-    <row r="373" spans="6:6" s="1" customFormat="1">
+    <row r="373" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F373" s="2"/>
     </row>
-    <row r="374" spans="6:6" s="1" customFormat="1">
+    <row r="374" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F374" s="2"/>
     </row>
-    <row r="375" spans="6:6" s="1" customFormat="1">
+    <row r="375" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F375" s="2"/>
     </row>
-    <row r="376" spans="6:6" s="1" customFormat="1">
+    <row r="376" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F376" s="2"/>
     </row>
-    <row r="377" spans="6:6" s="1" customFormat="1">
+    <row r="377" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F377" s="2"/>
     </row>
-    <row r="378" spans="6:6" s="1" customFormat="1">
+    <row r="378" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F378" s="2"/>
     </row>
-    <row r="379" spans="6:6" s="1" customFormat="1">
+    <row r="379" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F379" s="2"/>
     </row>
-    <row r="380" spans="6:6" s="1" customFormat="1">
+    <row r="380" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F380" s="2"/>
     </row>
-    <row r="381" spans="6:6" s="1" customFormat="1">
+    <row r="381" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F381" s="2"/>
     </row>
-    <row r="382" spans="6:6" s="1" customFormat="1">
+    <row r="382" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F382" s="2"/>
     </row>
-    <row r="383" spans="6:6" s="1" customFormat="1">
+    <row r="383" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F383" s="2"/>
     </row>
-    <row r="384" spans="6:6" s="1" customFormat="1">
+    <row r="384" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F384" s="2"/>
     </row>
-    <row r="385" spans="6:6" s="1" customFormat="1">
+    <row r="385" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F385" s="2"/>
     </row>
-    <row r="386" spans="6:6" s="1" customFormat="1">
+    <row r="386" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F386" s="2"/>
     </row>
-    <row r="387" spans="6:6" s="1" customFormat="1">
+    <row r="387" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F387" s="2"/>
     </row>
-    <row r="388" spans="6:6" s="1" customFormat="1">
+    <row r="388" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F388" s="2"/>
     </row>
-    <row r="389" spans="6:6" s="1" customFormat="1">
+    <row r="389" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F389" s="2"/>
     </row>
-    <row r="390" spans="6:6" s="1" customFormat="1">
+    <row r="390" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F390" s="2"/>
     </row>
-    <row r="391" spans="6:6" s="1" customFormat="1">
+    <row r="391" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F391" s="2"/>
     </row>
-    <row r="392" spans="6:6" s="1" customFormat="1">
+    <row r="392" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F392" s="2"/>
     </row>
-    <row r="393" spans="6:6" s="1" customFormat="1">
+    <row r="393" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F393" s="2"/>
     </row>
-    <row r="394" spans="6:6" s="1" customFormat="1">
+    <row r="394" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F394" s="2"/>
     </row>
-    <row r="395" spans="6:6" s="1" customFormat="1">
+    <row r="395" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F395" s="2"/>
     </row>
-    <row r="396" spans="6:6" s="1" customFormat="1">
+    <row r="396" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F396" s="2"/>
     </row>
-    <row r="397" spans="6:6" s="1" customFormat="1">
+    <row r="397" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F397" s="2"/>
     </row>
-    <row r="398" spans="6:6" s="1" customFormat="1">
+    <row r="398" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F398" s="2"/>
     </row>
-    <row r="399" spans="6:6" s="1" customFormat="1">
+    <row r="399" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F399" s="2"/>
     </row>
-    <row r="400" spans="6:6" s="1" customFormat="1">
+    <row r="400" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F400" s="2"/>
     </row>
-    <row r="401" spans="6:6" s="1" customFormat="1">
+    <row r="401" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F401" s="2"/>
     </row>
-    <row r="402" spans="6:6" s="1" customFormat="1">
+    <row r="402" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F402" s="2"/>
     </row>
-    <row r="403" spans="6:6" s="1" customFormat="1">
+    <row r="403" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F403" s="2"/>
     </row>
-    <row r="404" spans="6:6" s="1" customFormat="1">
+    <row r="404" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F404" s="2"/>
     </row>
-    <row r="405" spans="6:6" s="1" customFormat="1">
+    <row r="405" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F405" s="2"/>
     </row>
-    <row r="406" spans="6:6" s="1" customFormat="1">
+    <row r="406" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F406" s="2"/>
     </row>
-    <row r="407" spans="6:6" s="1" customFormat="1">
+    <row r="407" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F407" s="2"/>
     </row>
-    <row r="408" spans="6:6" s="1" customFormat="1">
+    <row r="408" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F408" s="2"/>
     </row>
-    <row r="409" spans="6:6" s="1" customFormat="1">
+    <row r="409" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F409" s="2"/>
     </row>
-    <row r="410" spans="6:6" s="1" customFormat="1">
+    <row r="410" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F410" s="2"/>
     </row>
-    <row r="411" spans="6:6" s="1" customFormat="1">
+    <row r="411" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F411" s="2"/>
     </row>
-    <row r="412" spans="6:6" s="1" customFormat="1">
+    <row r="412" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F412" s="2"/>
     </row>
-    <row r="413" spans="6:6" s="1" customFormat="1">
+    <row r="413" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F413" s="2"/>
     </row>
-    <row r="414" spans="6:6" s="1" customFormat="1">
+    <row r="414" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F414" s="2"/>
     </row>
-    <row r="415" spans="6:6" s="1" customFormat="1">
+    <row r="415" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F415" s="2"/>
     </row>
-    <row r="416" spans="6:6" s="1" customFormat="1">
+    <row r="416" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F416" s="2"/>
     </row>
-    <row r="417" spans="6:6" s="1" customFormat="1">
+    <row r="417" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F417" s="2"/>
     </row>
-    <row r="418" spans="6:6" s="1" customFormat="1">
+    <row r="418" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F418" s="2"/>
     </row>
-    <row r="419" spans="6:6" s="1" customFormat="1">
+    <row r="419" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F419" s="2"/>
     </row>
-    <row r="420" spans="6:6" s="1" customFormat="1">
+    <row r="420" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F420" s="2"/>
     </row>
-    <row r="421" spans="6:6" s="1" customFormat="1">
+    <row r="421" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F421" s="2"/>
     </row>
-    <row r="422" spans="6:6" s="1" customFormat="1">
+    <row r="422" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F422" s="2"/>
     </row>
-    <row r="423" spans="6:6" s="1" customFormat="1">
+    <row r="423" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F423" s="2"/>
     </row>
-    <row r="424" spans="6:6" s="1" customFormat="1">
+    <row r="424" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F424" s="2"/>
     </row>
-    <row r="425" spans="6:6" s="1" customFormat="1">
+    <row r="425" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F425" s="2"/>
     </row>
-    <row r="426" spans="6:6" s="1" customFormat="1">
+    <row r="426" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F426" s="2"/>
     </row>
-    <row r="427" spans="6:6" s="1" customFormat="1">
+    <row r="427" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F427" s="2"/>
     </row>
-    <row r="428" spans="6:6" s="1" customFormat="1">
+    <row r="428" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F428" s="2"/>
     </row>
-    <row r="429" spans="6:6" s="1" customFormat="1">
+    <row r="429" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F429" s="2"/>
     </row>
-    <row r="430" spans="6:6" s="1" customFormat="1">
+    <row r="430" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F430" s="2"/>
     </row>
-    <row r="431" spans="6:6" s="1" customFormat="1">
+    <row r="431" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F431" s="2"/>
     </row>
-    <row r="432" spans="6:6" s="1" customFormat="1">
+    <row r="432" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F432" s="2"/>
     </row>
-    <row r="433" spans="6:6" s="1" customFormat="1">
+    <row r="433" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F433" s="2"/>
     </row>
-    <row r="434" spans="6:6" s="1" customFormat="1">
+    <row r="434" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F434" s="2"/>
     </row>
-    <row r="435" spans="6:6" s="1" customFormat="1">
+    <row r="435" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F435" s="2"/>
     </row>
-    <row r="436" spans="6:6" s="1" customFormat="1">
+    <row r="436" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F436" s="2"/>
     </row>
-    <row r="437" spans="6:6" s="1" customFormat="1">
+    <row r="437" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F437" s="2"/>
     </row>
-    <row r="438" spans="6:6" s="1" customFormat="1">
+    <row r="438" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F438" s="2"/>
     </row>
-    <row r="439" spans="6:6" s="1" customFormat="1">
+    <row r="439" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F439" s="2"/>
     </row>
-    <row r="440" spans="6:6" s="1" customFormat="1">
+    <row r="440" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F440" s="2"/>
     </row>
-    <row r="441" spans="6:6" s="1" customFormat="1">
+    <row r="441" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F441" s="2"/>
     </row>
-    <row r="442" spans="6:6" s="1" customFormat="1">
+    <row r="442" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F442" s="2"/>
     </row>
-    <row r="443" spans="6:6" s="1" customFormat="1">
+    <row r="443" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F443" s="2"/>
     </row>
-    <row r="444" spans="6:6" s="1" customFormat="1">
+    <row r="444" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F444" s="2"/>
     </row>
-    <row r="445" spans="6:6" s="1" customFormat="1">
+    <row r="445" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F445" s="2"/>
     </row>
-    <row r="446" spans="6:6" s="1" customFormat="1">
+    <row r="446" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F446" s="2"/>
     </row>
-    <row r="447" spans="6:6" s="1" customFormat="1">
+    <row r="447" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F447" s="2"/>
     </row>
-    <row r="448" spans="6:6" s="1" customFormat="1">
+    <row r="448" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F448" s="2"/>
     </row>
-    <row r="449" spans="6:6" s="1" customFormat="1">
+    <row r="449" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F449" s="2"/>
     </row>
-    <row r="450" spans="6:6" s="1" customFormat="1">
+    <row r="450" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F450" s="2"/>
     </row>
-    <row r="451" spans="6:6" s="1" customFormat="1">
+    <row r="451" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F451" s="2"/>
     </row>
-    <row r="452" spans="6:6" s="1" customFormat="1">
+    <row r="452" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F452" s="2"/>
     </row>
-    <row r="453" spans="6:6" s="1" customFormat="1">
+    <row r="453" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F453" s="2"/>
     </row>
-    <row r="454" spans="6:6" s="1" customFormat="1">
+    <row r="454" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F454" s="2"/>
     </row>
-    <row r="455" spans="6:6" s="1" customFormat="1">
+    <row r="455" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F455" s="2"/>
     </row>
-    <row r="456" spans="6:6" s="1" customFormat="1">
+    <row r="456" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F456" s="2"/>
     </row>
-    <row r="457" spans="6:6" s="1" customFormat="1">
+    <row r="457" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F457" s="2"/>
     </row>
-    <row r="458" spans="6:6" s="1" customFormat="1">
+    <row r="458" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F458" s="2"/>
     </row>
-    <row r="459" spans="6:6" s="1" customFormat="1">
+    <row r="459" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F459" s="2"/>
     </row>
-    <row r="460" spans="6:6" s="1" customFormat="1">
+    <row r="460" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F460" s="2"/>
     </row>
-    <row r="461" spans="6:6" s="1" customFormat="1">
+    <row r="461" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F461" s="2"/>
     </row>
-    <row r="462" spans="6:6" s="1" customFormat="1">
+    <row r="462" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F462" s="2"/>
     </row>
-    <row r="463" spans="6:6" s="1" customFormat="1">
+    <row r="463" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F463" s="2"/>
     </row>
-    <row r="464" spans="6:6" s="1" customFormat="1">
+    <row r="464" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F464" s="2"/>
     </row>
-    <row r="465" spans="6:6" s="1" customFormat="1">
+    <row r="465" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F465" s="2"/>
     </row>
-    <row r="466" spans="6:6" s="1" customFormat="1">
+    <row r="466" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F466" s="2"/>
     </row>
-    <row r="467" spans="6:6" s="1" customFormat="1">
+    <row r="467" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F467" s="2"/>
     </row>
-    <row r="468" spans="6:6" s="1" customFormat="1">
+    <row r="468" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F468" s="2"/>
     </row>
-    <row r="469" spans="6:6" s="1" customFormat="1">
+    <row r="469" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F469" s="2"/>
     </row>
-    <row r="470" spans="6:6" s="1" customFormat="1">
+    <row r="470" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F470" s="2"/>
     </row>
-    <row r="471" spans="6:6" s="1" customFormat="1">
+    <row r="471" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F471" s="2"/>
     </row>
-    <row r="472" spans="6:6" s="1" customFormat="1">
+    <row r="472" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F472" s="2"/>
     </row>
-    <row r="473" spans="6:6" s="1" customFormat="1">
+    <row r="473" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F473" s="2"/>
     </row>
-    <row r="474" spans="6:6" s="1" customFormat="1">
+    <row r="474" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F474" s="2"/>
     </row>
-    <row r="475" spans="6:6" s="1" customFormat="1">
+    <row r="475" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F475" s="2"/>
     </row>
-    <row r="476" spans="6:6" s="1" customFormat="1">
+    <row r="476" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F476" s="2"/>
     </row>
-    <row r="477" spans="6:6" s="1" customFormat="1">
+    <row r="477" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F477" s="2"/>
     </row>
-    <row r="478" spans="6:6" s="1" customFormat="1">
+    <row r="478" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F478" s="2"/>
     </row>
-    <row r="479" spans="6:6" s="1" customFormat="1">
+    <row r="479" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F479" s="2"/>
     </row>
-    <row r="480" spans="6:6" s="1" customFormat="1">
+    <row r="480" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F480" s="2"/>
     </row>
-    <row r="481" spans="6:6" s="1" customFormat="1">
+    <row r="481" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F481" s="2"/>
     </row>
-    <row r="482" spans="6:6" s="1" customFormat="1">
+    <row r="482" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F482" s="2"/>
     </row>
-    <row r="483" spans="6:6" s="1" customFormat="1">
+    <row r="483" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F483" s="2"/>
     </row>
-    <row r="484" spans="6:6" s="1" customFormat="1">
+    <row r="484" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F484" s="2"/>
     </row>
-    <row r="485" spans="6:6" s="1" customFormat="1">
+    <row r="485" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F485" s="2"/>
     </row>
-    <row r="486" spans="6:6" s="1" customFormat="1">
+    <row r="486" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F486" s="2"/>
     </row>
-    <row r="487" spans="6:6" s="1" customFormat="1">
+    <row r="487" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F487" s="2"/>
     </row>
-    <row r="488" spans="6:6" s="1" customFormat="1">
+    <row r="488" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F488" s="2"/>
     </row>
-    <row r="489" spans="6:6" s="1" customFormat="1">
+    <row r="489" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F489" s="2"/>
     </row>
-    <row r="490" spans="6:6" s="1" customFormat="1">
+    <row r="490" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F490" s="2"/>
     </row>
-    <row r="491" spans="6:6" s="1" customFormat="1">
+    <row r="491" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F491" s="2"/>
     </row>
-    <row r="492" spans="6:6" s="1" customFormat="1">
+    <row r="492" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F492" s="2"/>
     </row>
-    <row r="493" spans="6:6" s="1" customFormat="1">
+    <row r="493" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F493" s="2"/>
     </row>
-    <row r="494" spans="6:6" s="1" customFormat="1">
+    <row r="494" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F494" s="2"/>
     </row>
-    <row r="495" spans="6:6" s="1" customFormat="1">
+    <row r="495" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F495" s="2"/>
     </row>
-    <row r="496" spans="6:6" s="1" customFormat="1">
+    <row r="496" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F496" s="2"/>
     </row>
-    <row r="497" spans="6:6" s="1" customFormat="1">
+    <row r="497" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F497" s="2"/>
     </row>
-    <row r="498" spans="6:6" s="1" customFormat="1">
+    <row r="498" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F498" s="2"/>
     </row>
-    <row r="499" spans="6:6" s="1" customFormat="1">
+    <row r="499" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F499" s="2"/>
     </row>
-    <row r="500" spans="6:6" s="1" customFormat="1">
+    <row r="500" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F500" s="2"/>
     </row>
-    <row r="501" spans="6:6" s="1" customFormat="1">
+    <row r="501" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F501" s="2"/>
     </row>
-    <row r="502" spans="6:6" s="1" customFormat="1">
+    <row r="502" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F502" s="2"/>
     </row>
-    <row r="503" spans="6:6" s="1" customFormat="1">
+    <row r="503" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F503" s="2"/>
     </row>
-    <row r="504" spans="6:6" s="1" customFormat="1">
+    <row r="504" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F504" s="2"/>
     </row>
-    <row r="505" spans="6:6" s="1" customFormat="1">
+    <row r="505" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F505" s="2"/>
     </row>
-    <row r="506" spans="6:6" s="1" customFormat="1">
+    <row r="506" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F506" s="2"/>
     </row>
-    <row r="507" spans="6:6" s="1" customFormat="1">
+    <row r="507" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F507" s="2"/>
     </row>
-    <row r="508" spans="6:6" s="1" customFormat="1">
+    <row r="508" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F508" s="2"/>
     </row>
-    <row r="509" spans="6:6" s="1" customFormat="1">
+    <row r="509" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F509" s="2"/>
     </row>
-    <row r="510" spans="6:6" s="1" customFormat="1">
+    <row r="510" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F510" s="2"/>
     </row>
-    <row r="511" spans="6:6" s="1" customFormat="1">
+    <row r="511" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F511" s="2"/>
     </row>
-    <row r="512" spans="6:6" s="1" customFormat="1">
+    <row r="512" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F512" s="2"/>
     </row>
-    <row r="513" spans="6:6" s="1" customFormat="1">
+    <row r="513" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F513" s="2"/>
     </row>
-    <row r="514" spans="6:6" s="1" customFormat="1">
+    <row r="514" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F514" s="2"/>
     </row>
-    <row r="515" spans="6:6" s="1" customFormat="1">
+    <row r="515" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F515" s="2"/>
     </row>
-    <row r="516" spans="6:6" s="1" customFormat="1">
+    <row r="516" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F516" s="2"/>
     </row>
-    <row r="517" spans="6:6" s="1" customFormat="1">
+    <row r="517" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F517" s="2"/>
     </row>
-    <row r="518" spans="6:6" s="1" customFormat="1">
+    <row r="518" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F518" s="2"/>
     </row>
-    <row r="519" spans="6:6" s="1" customFormat="1">
+    <row r="519" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F519" s="2"/>
     </row>
-    <row r="520" spans="6:6" s="1" customFormat="1">
+    <row r="520" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F520" s="2"/>
     </row>
-    <row r="521" spans="6:6" s="1" customFormat="1">
+    <row r="521" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F521" s="2"/>
     </row>
-    <row r="522" spans="6:6" s="1" customFormat="1">
+    <row r="522" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F522" s="2"/>
     </row>
-    <row r="523" spans="6:6" s="1" customFormat="1">
+    <row r="523" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F523" s="2"/>
     </row>
-    <row r="524" spans="6:6" s="1" customFormat="1">
+    <row r="524" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F524" s="2"/>
     </row>
-    <row r="525" spans="6:6" s="1" customFormat="1">
+    <row r="525" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F525" s="2"/>
     </row>
-    <row r="526" spans="6:6" s="1" customFormat="1">
+    <row r="526" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F526" s="2"/>
     </row>
-    <row r="527" spans="6:6" s="1" customFormat="1">
+    <row r="527" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F527" s="2"/>
     </row>
-    <row r="528" spans="6:6" s="1" customFormat="1">
+    <row r="528" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F528" s="2"/>
     </row>
-    <row r="529" spans="6:6" s="1" customFormat="1">
+    <row r="529" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F529" s="2"/>
     </row>
-    <row r="530" spans="6:6" s="1" customFormat="1">
+    <row r="530" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F530" s="2"/>
     </row>
-    <row r="531" spans="6:6" s="1" customFormat="1">
+    <row r="531" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F531" s="2"/>
     </row>
-    <row r="532" spans="6:6" s="1" customFormat="1">
+    <row r="532" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F532" s="2"/>
     </row>
-    <row r="533" spans="6:6" s="1" customFormat="1">
+    <row r="533" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F533" s="2"/>
     </row>
-    <row r="534" spans="6:6" s="1" customFormat="1">
+    <row r="534" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F534" s="2"/>
     </row>
-    <row r="535" spans="6:6" s="1" customFormat="1">
+    <row r="535" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F535" s="2"/>
     </row>
-    <row r="536" spans="6:6" s="1" customFormat="1">
+    <row r="536" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F536" s="2"/>
     </row>
-    <row r="537" spans="6:6" s="1" customFormat="1">
+    <row r="537" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F537" s="2"/>
     </row>
-    <row r="538" spans="6:6" s="1" customFormat="1">
+    <row r="538" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F538" s="2"/>
     </row>
-    <row r="539" spans="6:6" s="1" customFormat="1">
+    <row r="539" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F539" s="2"/>
     </row>
-    <row r="540" spans="6:6" s="1" customFormat="1">
+    <row r="540" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F540" s="2"/>
     </row>
-    <row r="541" spans="6:6" s="1" customFormat="1">
+    <row r="541" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F541" s="2"/>
     </row>
-    <row r="542" spans="6:6" s="1" customFormat="1">
+    <row r="542" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F542" s="2"/>
     </row>
-    <row r="543" spans="6:6" s="1" customFormat="1">
+    <row r="543" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F543" s="2"/>
     </row>
-    <row r="544" spans="6:6" s="1" customFormat="1">
+    <row r="544" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F544" s="2"/>
     </row>
-    <row r="545" spans="6:6" s="1" customFormat="1">
+    <row r="545" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F545" s="2"/>
     </row>
-    <row r="546" spans="6:6" s="1" customFormat="1">
+    <row r="546" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F546" s="2"/>
     </row>
-    <row r="547" spans="6:6" s="1" customFormat="1">
+    <row r="547" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F547" s="2"/>
     </row>
-    <row r="548" spans="6:6" s="1" customFormat="1">
+    <row r="548" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F548" s="2"/>
     </row>
-    <row r="549" spans="6:6" s="1" customFormat="1">
+    <row r="549" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F549" s="2"/>
     </row>
-    <row r="550" spans="6:6" s="1" customFormat="1">
+    <row r="550" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F550" s="2"/>
     </row>
-    <row r="551" spans="6:6" s="1" customFormat="1">
+    <row r="551" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F551" s="2"/>
     </row>
-    <row r="552" spans="6:6" s="1" customFormat="1">
+    <row r="552" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F552" s="2"/>
     </row>
-    <row r="553" spans="6:6" s="1" customFormat="1">
+    <row r="553" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F553" s="2"/>
     </row>
-    <row r="554" spans="6:6" s="1" customFormat="1">
+    <row r="554" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F554" s="2"/>
     </row>
-    <row r="555" spans="6:6" s="1" customFormat="1">
+    <row r="555" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F555" s="2"/>
     </row>
-    <row r="556" spans="6:6" s="1" customFormat="1">
+    <row r="556" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F556" s="2"/>
     </row>
-    <row r="557" spans="6:6" s="1" customFormat="1">
+    <row r="557" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F557" s="2"/>
     </row>
-    <row r="558" spans="6:6" s="1" customFormat="1">
+    <row r="558" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F558" s="2"/>
     </row>
-    <row r="559" spans="6:6" s="1" customFormat="1">
+    <row r="559" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F559" s="2"/>
     </row>
-    <row r="560" spans="6:6" s="1" customFormat="1">
+    <row r="560" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F560" s="2"/>
     </row>
-    <row r="561" spans="6:6" s="1" customFormat="1">
+    <row r="561" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F561" s="2"/>
     </row>
-    <row r="562" spans="6:6" s="1" customFormat="1">
+    <row r="562" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F562" s="2"/>
     </row>
-    <row r="563" spans="6:6" s="1" customFormat="1">
+    <row r="563" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F563" s="2"/>
     </row>
-    <row r="564" spans="6:6" s="1" customFormat="1">
+    <row r="564" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F564" s="2"/>
     </row>
-    <row r="565" spans="6:6" s="1" customFormat="1">
+    <row r="565" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F565" s="2"/>
     </row>
-    <row r="566" spans="6:6" s="1" customFormat="1">
+    <row r="566" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F566" s="2"/>
     </row>
-    <row r="567" spans="6:6" s="1" customFormat="1">
+    <row r="567" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F567" s="2"/>
     </row>
-    <row r="568" spans="6:6" s="1" customFormat="1">
+    <row r="568" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F568" s="2"/>
     </row>
-    <row r="569" spans="6:6" s="1" customFormat="1">
+    <row r="569" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F569" s="2"/>
     </row>
-    <row r="570" spans="6:6" s="1" customFormat="1">
+    <row r="570" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F570" s="2"/>
     </row>
-    <row r="571" spans="6:6" s="1" customFormat="1">
+    <row r="571" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F571" s="2"/>
     </row>
-    <row r="572" spans="6:6" s="1" customFormat="1">
+    <row r="572" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F572" s="2"/>
     </row>
-    <row r="573" spans="6:6" s="1" customFormat="1">
+    <row r="573" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F573" s="2"/>
     </row>
-    <row r="574" spans="6:6" s="1" customFormat="1">
+    <row r="574" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F574" s="2"/>
     </row>
-    <row r="575" spans="6:6" s="1" customFormat="1">
+    <row r="575" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F575" s="2"/>
     </row>
-    <row r="576" spans="6:6" s="1" customFormat="1">
+    <row r="576" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F576" s="2"/>
     </row>
-    <row r="577" spans="6:6" s="1" customFormat="1">
+    <row r="577" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F577" s="2"/>
     </row>
-    <row r="578" spans="6:6" s="1" customFormat="1">
+    <row r="578" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F578" s="2"/>
     </row>
-    <row r="579" spans="6:6" s="1" customFormat="1">
+    <row r="579" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F579" s="2"/>
     </row>
-    <row r="580" spans="6:6" s="1" customFormat="1">
+    <row r="580" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F580" s="2"/>
     </row>
-    <row r="581" spans="6:6" s="1" customFormat="1">
+    <row r="581" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F581" s="2"/>
     </row>
-    <row r="582" spans="6:6" s="1" customFormat="1">
+    <row r="582" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F582" s="2"/>
     </row>
-    <row r="583" spans="6:6" s="1" customFormat="1">
+    <row r="583" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F583" s="2"/>
     </row>
-    <row r="584" spans="6:6" s="1" customFormat="1">
+    <row r="584" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F584" s="2"/>
     </row>
-    <row r="585" spans="6:6" s="1" customFormat="1">
+    <row r="585" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F585" s="2"/>
     </row>
-    <row r="586" spans="6:6" s="1" customFormat="1">
+    <row r="586" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F586" s="2"/>
     </row>
-    <row r="587" spans="6:6" s="1" customFormat="1">
+    <row r="587" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F587" s="2"/>
     </row>
-    <row r="588" spans="6:6" s="1" customFormat="1">
+    <row r="588" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F588" s="2"/>
     </row>
-    <row r="589" spans="6:6" s="1" customFormat="1">
+    <row r="589" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F589" s="2"/>
     </row>
-    <row r="590" spans="6:6" s="1" customFormat="1">
+    <row r="590" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F590" s="2"/>
     </row>
-    <row r="591" spans="6:6" s="1" customFormat="1">
+    <row r="591" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F591" s="2"/>
     </row>
-    <row r="592" spans="6:6" s="1" customFormat="1">
+    <row r="592" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F592" s="2"/>
     </row>
-    <row r="593" spans="6:6" s="1" customFormat="1">
+    <row r="593" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F593" s="2"/>
     </row>
-    <row r="594" spans="6:6" s="1" customFormat="1">
+    <row r="594" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F594" s="2"/>
     </row>
-    <row r="595" spans="6:6" s="1" customFormat="1">
+    <row r="595" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F595" s="2"/>
     </row>
-    <row r="596" spans="6:6" s="1" customFormat="1">
+    <row r="596" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F596" s="2"/>
     </row>
-    <row r="597" spans="6:6" s="1" customFormat="1">
+    <row r="597" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F597" s="2"/>
     </row>
-    <row r="598" spans="6:6" s="1" customFormat="1">
+    <row r="598" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F598" s="2"/>
     </row>
-    <row r="599" spans="6:6" s="1" customFormat="1">
+    <row r="599" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F599" s="2"/>
     </row>
-    <row r="600" spans="6:6" s="1" customFormat="1">
+    <row r="600" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F600" s="2"/>
     </row>
-    <row r="601" spans="6:6" s="1" customFormat="1">
+    <row r="601" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F601" s="2"/>
     </row>
-    <row r="602" spans="6:6" s="1" customFormat="1">
+    <row r="602" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F602" s="2"/>
     </row>
-    <row r="603" spans="6:6" s="1" customFormat="1">
+    <row r="603" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F603" s="2"/>
     </row>
-    <row r="604" spans="6:6" s="1" customFormat="1">
+    <row r="604" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F604" s="2"/>
     </row>
-    <row r="605" spans="6:6" s="1" customFormat="1">
+    <row r="605" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F605" s="2"/>
     </row>
-    <row r="606" spans="6:6" s="1" customFormat="1">
+    <row r="606" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F606" s="2"/>
     </row>
-    <row r="607" spans="6:6" s="1" customFormat="1">
+    <row r="607" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F607" s="2"/>
     </row>
-    <row r="608" spans="6:6" s="1" customFormat="1">
+    <row r="608" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F608" s="2"/>
     </row>
-    <row r="609" spans="6:6" s="1" customFormat="1">
+    <row r="609" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F609" s="2"/>
     </row>
-    <row r="610" spans="6:6" s="1" customFormat="1">
+    <row r="610" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F610" s="2"/>
     </row>
-    <row r="611" spans="6:6" s="1" customFormat="1">
+    <row r="611" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F611" s="2"/>
     </row>
-    <row r="612" spans="6:6" s="1" customFormat="1">
+    <row r="612" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F612" s="2"/>
     </row>
-    <row r="613" spans="6:6" s="1" customFormat="1">
+    <row r="613" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F613" s="2"/>
     </row>
-    <row r="614" spans="6:6" s="1" customFormat="1">
+    <row r="614" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F614" s="2"/>
     </row>
-    <row r="615" spans="6:6" s="1" customFormat="1">
+    <row r="615" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F615" s="2"/>
     </row>
-    <row r="616" spans="6:6" s="1" customFormat="1">
+    <row r="616" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F616" s="2"/>
     </row>
-    <row r="617" spans="6:6" s="1" customFormat="1">
+    <row r="617" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F617" s="2"/>
     </row>
-    <row r="618" spans="6:6" s="1" customFormat="1">
+    <row r="618" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F618" s="2"/>
     </row>
-    <row r="619" spans="6:6" s="1" customFormat="1">
+    <row r="619" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F619" s="2"/>
     </row>
-    <row r="620" spans="6:6" s="1" customFormat="1">
+    <row r="620" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F620" s="2"/>
     </row>
-    <row r="621" spans="6:6" s="1" customFormat="1">
+    <row r="621" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F621" s="2"/>
     </row>
-    <row r="622" spans="6:6" s="1" customFormat="1">
+    <row r="622" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F622" s="2"/>
     </row>
-    <row r="623" spans="6:6" s="1" customFormat="1">
+    <row r="623" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F623" s="2"/>
     </row>
-    <row r="624" spans="6:6" s="1" customFormat="1">
+    <row r="624" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F624" s="2"/>
     </row>
-    <row r="625" spans="6:6" s="1" customFormat="1">
+    <row r="625" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F625" s="2"/>
     </row>
-    <row r="626" spans="6:6" s="1" customFormat="1">
+    <row r="626" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F626" s="2"/>
     </row>
-    <row r="627" spans="6:6" s="1" customFormat="1">
+    <row r="627" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F627" s="2"/>
     </row>
-    <row r="628" spans="6:6" s="1" customFormat="1">
+    <row r="628" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F628" s="2"/>
     </row>
-    <row r="629" spans="6:6" s="1" customFormat="1">
+    <row r="629" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F629" s="2"/>
     </row>
-    <row r="630" spans="6:6" s="1" customFormat="1">
+    <row r="630" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F630" s="2"/>
     </row>
-    <row r="631" spans="6:6" s="1" customFormat="1">
+    <row r="631" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F631" s="2"/>
     </row>
-    <row r="632" spans="6:6" s="1" customFormat="1">
+    <row r="632" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F632" s="2"/>
     </row>
-    <row r="633" spans="6:6" s="1" customFormat="1">
+    <row r="633" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F633" s="2"/>
     </row>
-    <row r="634" spans="6:6" s="1" customFormat="1">
+    <row r="634" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F634" s="2"/>
     </row>
-    <row r="635" spans="6:6" s="1" customFormat="1">
+    <row r="635" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F635" s="2"/>
     </row>
-    <row r="636" spans="6:6" s="1" customFormat="1">
+    <row r="636" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F636" s="2"/>
     </row>
-    <row r="637" spans="6:6" s="1" customFormat="1">
+    <row r="637" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F637" s="2"/>
     </row>
-    <row r="638" spans="6:6" s="1" customFormat="1">
+    <row r="638" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F638" s="2"/>
     </row>
-    <row r="639" spans="6:6" s="1" customFormat="1">
+    <row r="639" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F639" s="2"/>
     </row>
-    <row r="640" spans="6:6" s="1" customFormat="1">
+    <row r="640" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F640" s="2"/>
     </row>
-    <row r="641" spans="6:6" s="1" customFormat="1">
+    <row r="641" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F641" s="2"/>
     </row>
-    <row r="642" spans="6:6" s="1" customFormat="1">
+    <row r="642" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F642" s="2"/>
     </row>
-    <row r="643" spans="6:6" s="1" customFormat="1">
+    <row r="643" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F643" s="2"/>
     </row>
-    <row r="644" spans="6:6" s="1" customFormat="1">
+    <row r="644" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F644" s="2"/>
     </row>
-    <row r="645" spans="6:6" s="1" customFormat="1">
+    <row r="645" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F645" s="2"/>
     </row>
-    <row r="646" spans="6:6" s="1" customFormat="1">
+    <row r="646" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F646" s="2"/>
     </row>
-    <row r="647" spans="6:6" s="1" customFormat="1">
+    <row r="647" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F647" s="2"/>
     </row>
-    <row r="648" spans="6:6" s="1" customFormat="1">
+    <row r="648" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F648" s="2"/>
     </row>
-    <row r="649" spans="6:6" s="1" customFormat="1">
+    <row r="649" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F649" s="2"/>
     </row>
-    <row r="650" spans="6:6" s="1" customFormat="1">
+    <row r="650" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F650" s="2"/>
     </row>
-    <row r="651" spans="6:6" s="1" customFormat="1">
+    <row r="651" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F651" s="2"/>
     </row>
-    <row r="652" spans="6:6" s="1" customFormat="1">
+    <row r="652" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F652" s="2"/>
     </row>
-    <row r="653" spans="6:6" s="1" customFormat="1">
+    <row r="653" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F653" s="2"/>
     </row>
-    <row r="654" spans="6:6" s="1" customFormat="1">
+    <row r="654" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F654" s="2"/>
     </row>
-    <row r="655" spans="6:6" s="1" customFormat="1">
+    <row r="655" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F655" s="2"/>
     </row>
-    <row r="656" spans="6:6" s="1" customFormat="1">
+    <row r="656" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F656" s="2"/>
     </row>
-    <row r="657" spans="6:6" s="1" customFormat="1">
+    <row r="657" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F657" s="2"/>
     </row>
-    <row r="658" spans="6:6" s="1" customFormat="1">
+    <row r="658" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F658" s="2"/>
     </row>
-    <row r="659" spans="6:6" s="1" customFormat="1">
+    <row r="659" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F659" s="2"/>
     </row>
-    <row r="660" spans="6:6" s="1" customFormat="1">
+    <row r="660" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F660" s="2"/>
     </row>
-    <row r="661" spans="6:6" s="1" customFormat="1">
+    <row r="661" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F661" s="2"/>
     </row>
-    <row r="662" spans="6:6" s="1" customFormat="1">
+    <row r="662" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F662" s="2"/>
     </row>
-    <row r="663" spans="6:6" s="1" customFormat="1">
+    <row r="663" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F663" s="2"/>
     </row>
-    <row r="664" spans="6:6" s="1" customFormat="1">
+    <row r="664" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F664" s="2"/>
     </row>
-    <row r="665" spans="6:6" s="1" customFormat="1">
+    <row r="665" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F665" s="2"/>
     </row>
-    <row r="666" spans="6:6" s="1" customFormat="1">
+    <row r="666" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F666" s="2"/>
     </row>
-    <row r="667" spans="6:6" s="1" customFormat="1">
+    <row r="667" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F667" s="2"/>
     </row>
-    <row r="668" spans="6:6" s="1" customFormat="1">
+    <row r="668" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F668" s="2"/>
     </row>
-    <row r="669" spans="6:6" s="1" customFormat="1">
+    <row r="669" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F669" s="2"/>
     </row>
-    <row r="670" spans="6:6" s="1" customFormat="1">
+    <row r="670" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F670" s="2"/>
     </row>
-    <row r="671" spans="6:6" s="1" customFormat="1">
+    <row r="671" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F671" s="2"/>
     </row>
-    <row r="672" spans="6:6" s="1" customFormat="1">
+    <row r="672" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F672" s="2"/>
     </row>
-    <row r="673" spans="6:6" s="1" customFormat="1">
+    <row r="673" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F673" s="2"/>
     </row>
-    <row r="674" spans="6:6" s="1" customFormat="1">
+    <row r="674" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F674" s="2"/>
     </row>
-    <row r="675" spans="6:6" s="1" customFormat="1">
+    <row r="675" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F675" s="2"/>
     </row>
-    <row r="676" spans="6:6" s="1" customFormat="1">
+    <row r="676" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F676" s="2"/>
     </row>
-    <row r="677" spans="6:6" s="1" customFormat="1">
+    <row r="677" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F677" s="2"/>
     </row>
-    <row r="678" spans="6:6" s="1" customFormat="1">
+    <row r="678" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F678" s="2"/>
     </row>
-    <row r="679" spans="6:6" s="1" customFormat="1">
+    <row r="679" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F679" s="2"/>
     </row>
-    <row r="680" spans="6:6" s="1" customFormat="1">
+    <row r="680" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F680" s="2"/>
     </row>
-    <row r="681" spans="6:6" s="1" customFormat="1">
+    <row r="681" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F681" s="2"/>
     </row>
-    <row r="682" spans="6:6" s="1" customFormat="1">
+    <row r="682" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F682" s="2"/>
     </row>
-    <row r="683" spans="6:6" s="1" customFormat="1">
+    <row r="683" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F683" s="2"/>
     </row>
-    <row r="684" spans="6:6" s="1" customFormat="1">
+    <row r="684" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F684" s="2"/>
     </row>
-    <row r="685" spans="6:6" s="1" customFormat="1">
+    <row r="685" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F685" s="2"/>
     </row>
-    <row r="686" spans="6:6" s="1" customFormat="1">
+    <row r="686" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F686" s="2"/>
     </row>
-    <row r="687" spans="6:6" s="1" customFormat="1">
+    <row r="687" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F687" s="2"/>
     </row>
-    <row r="688" spans="6:6" s="1" customFormat="1">
+    <row r="688" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F688" s="2"/>
     </row>
-    <row r="689" spans="6:6" s="1" customFormat="1">
+    <row r="689" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F689" s="2"/>
     </row>
-    <row r="690" spans="6:6" s="1" customFormat="1">
+    <row r="690" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F690" s="2"/>
     </row>
-    <row r="691" spans="6:6" s="1" customFormat="1">
+    <row r="691" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F691" s="2"/>
     </row>
-    <row r="692" spans="6:6" s="1" customFormat="1">
+    <row r="692" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F692" s="2"/>
     </row>
-    <row r="693" spans="6:6" s="1" customFormat="1">
+    <row r="693" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F693" s="2"/>
     </row>
-    <row r="694" spans="6:6" s="1" customFormat="1">
+    <row r="694" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F694" s="2"/>
     </row>
-    <row r="695" spans="6:6" s="1" customFormat="1">
+    <row r="695" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F695" s="2"/>
     </row>
-    <row r="696" spans="6:6" s="1" customFormat="1">
+    <row r="696" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F696" s="2"/>
     </row>
-    <row r="697" spans="6:6" s="1" customFormat="1">
+    <row r="697" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F697" s="2"/>
     </row>
-    <row r="698" spans="6:6" s="1" customFormat="1">
+    <row r="698" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F698" s="2"/>
     </row>
-    <row r="699" spans="6:6" s="1" customFormat="1">
+    <row r="699" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F699" s="2"/>
     </row>
-    <row r="700" spans="6:6" s="1" customFormat="1">
+    <row r="700" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F700" s="2"/>
     </row>
-    <row r="701" spans="6:6" s="1" customFormat="1">
+    <row r="701" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F701" s="2"/>
     </row>
-    <row r="702" spans="6:6" s="1" customFormat="1">
+    <row r="702" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F702" s="2"/>
     </row>
-    <row r="703" spans="6:6" s="1" customFormat="1">
+    <row r="703" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F703" s="2"/>
     </row>
-    <row r="704" spans="6:6" s="1" customFormat="1">
+    <row r="704" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F704" s="2"/>
     </row>
-    <row r="705" spans="6:6" s="1" customFormat="1">
+    <row r="705" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F705" s="2"/>
     </row>
-    <row r="706" spans="6:6" s="1" customFormat="1">
+    <row r="706" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F706" s="2"/>
     </row>
-    <row r="707" spans="6:6" s="1" customFormat="1">
+    <row r="707" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F707" s="2"/>
     </row>
-    <row r="708" spans="6:6" s="1" customFormat="1">
+    <row r="708" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F708" s="2"/>
     </row>
-    <row r="709" spans="6:6" s="1" customFormat="1">
+    <row r="709" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F709" s="2"/>
     </row>
-    <row r="710" spans="6:6" s="1" customFormat="1">
+    <row r="710" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F710" s="2"/>
     </row>
-    <row r="711" spans="6:6" s="1" customFormat="1">
+    <row r="711" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F711" s="2"/>
     </row>
-    <row r="712" spans="6:6" s="1" customFormat="1">
+    <row r="712" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F712" s="2"/>
     </row>
-    <row r="713" spans="6:6" s="1" customFormat="1">
+    <row r="713" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F713" s="2"/>
     </row>
-    <row r="714" spans="6:6" s="1" customFormat="1">
+    <row r="714" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F714" s="2"/>
     </row>
-    <row r="715" spans="6:6" s="1" customFormat="1">
+    <row r="715" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F715" s="2"/>
     </row>
-    <row r="716" spans="6:6" s="1" customFormat="1">
+    <row r="716" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F716" s="2"/>
     </row>
-    <row r="717" spans="6:6" s="1" customFormat="1">
+    <row r="717" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F717" s="2"/>
     </row>
-    <row r="718" spans="6:6" s="1" customFormat="1">
+    <row r="718" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F718" s="2"/>
     </row>
-    <row r="719" spans="6:6" s="1" customFormat="1">
+    <row r="719" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F719" s="2"/>
     </row>
-    <row r="720" spans="6:6" s="1" customFormat="1">
+    <row r="720" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F720" s="2"/>
     </row>
-    <row r="721" spans="6:6" s="1" customFormat="1">
+    <row r="721" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F721" s="2"/>
     </row>
-    <row r="722" spans="6:6" s="1" customFormat="1">
+    <row r="722" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F722" s="2"/>
     </row>
-    <row r="723" spans="6:6" s="1" customFormat="1">
+    <row r="723" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F723" s="2"/>
     </row>
-    <row r="724" spans="6:6" s="1" customFormat="1">
+    <row r="724" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F724" s="2"/>
     </row>
-    <row r="725" spans="6:6" s="1" customFormat="1">
+    <row r="725" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F725" s="2"/>
     </row>
-    <row r="726" spans="6:6" s="1" customFormat="1">
+    <row r="726" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F726" s="2"/>
     </row>
-    <row r="727" spans="6:6" s="1" customFormat="1">
+    <row r="727" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F727" s="2"/>
     </row>
-    <row r="728" spans="6:6" s="1" customFormat="1">
+    <row r="728" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F728" s="2"/>
     </row>
-    <row r="729" spans="6:6" s="1" customFormat="1">
+    <row r="729" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F729" s="2"/>
     </row>
-    <row r="730" spans="6:6" s="1" customFormat="1">
+    <row r="730" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F730" s="2"/>
     </row>
-    <row r="731" spans="6:6" s="1" customFormat="1">
+    <row r="731" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F731" s="2"/>
     </row>
-    <row r="732" spans="6:6" s="1" customFormat="1">
+    <row r="732" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F732" s="2"/>
     </row>
-    <row r="733" spans="6:6" s="1" customFormat="1">
+    <row r="733" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F733" s="2"/>
     </row>
-    <row r="734" spans="6:6" s="1" customFormat="1">
+    <row r="734" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F734" s="2"/>
     </row>
-    <row r="735" spans="6:6" s="1" customFormat="1">
+    <row r="735" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F735" s="2"/>
     </row>
-    <row r="736" spans="6:6" s="1" customFormat="1">
+    <row r="736" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F736" s="2"/>
     </row>
-    <row r="737" spans="6:6" s="1" customFormat="1">
+    <row r="737" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F737" s="2"/>
     </row>
-    <row r="738" spans="6:6" s="1" customFormat="1">
+    <row r="738" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F738" s="2"/>
     </row>
-    <row r="739" spans="6:6" s="1" customFormat="1">
+    <row r="739" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F739" s="2"/>
     </row>
-    <row r="740" spans="6:6" s="1" customFormat="1">
+    <row r="740" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F740" s="2"/>
     </row>
-    <row r="741" spans="6:6" s="1" customFormat="1">
+    <row r="741" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F741" s="2"/>
     </row>
-    <row r="742" spans="6:6" s="1" customFormat="1">
+    <row r="742" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F742" s="2"/>
     </row>
-    <row r="743" spans="6:6" s="1" customFormat="1">
+    <row r="743" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F743" s="2"/>
     </row>
-    <row r="744" spans="6:6" s="1" customFormat="1">
+    <row r="744" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F744" s="2"/>
     </row>
-    <row r="745" spans="6:6" s="1" customFormat="1">
+    <row r="745" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F745" s="2"/>
     </row>
-    <row r="746" spans="6:6" s="1" customFormat="1">
+    <row r="746" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F746" s="2"/>
     </row>
-    <row r="747" spans="6:6" s="1" customFormat="1">
+    <row r="747" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F747" s="2"/>
     </row>
-    <row r="748" spans="6:6" s="1" customFormat="1">
+    <row r="748" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F748" s="2"/>
     </row>
-    <row r="749" spans="6:6" s="1" customFormat="1">
+    <row r="749" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F749" s="2"/>
     </row>
-    <row r="750" spans="6:6" s="1" customFormat="1">
+    <row r="750" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F750" s="2"/>
     </row>
-    <row r="751" spans="6:6" s="1" customFormat="1">
+    <row r="751" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F751" s="2"/>
     </row>
-    <row r="752" spans="6:6" s="1" customFormat="1">
+    <row r="752" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F752" s="2"/>
     </row>
-    <row r="753" spans="6:6" s="1" customFormat="1">
+    <row r="753" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F753" s="2"/>
     </row>
-    <row r="754" spans="6:6" s="1" customFormat="1">
+    <row r="754" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F754" s="2"/>
     </row>
-    <row r="755" spans="6:6" s="1" customFormat="1">
+    <row r="755" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F755" s="2"/>
     </row>
-    <row r="756" spans="6:6" s="1" customFormat="1">
+    <row r="756" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F756" s="2"/>
     </row>
-    <row r="757" spans="6:6" s="1" customFormat="1">
+    <row r="757" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F757" s="2"/>
     </row>
-    <row r="758" spans="6:6" s="1" customFormat="1">
+    <row r="758" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F758" s="2"/>
     </row>
-    <row r="759" spans="6:6" s="1" customFormat="1">
+    <row r="759" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F759" s="2"/>
     </row>
-    <row r="760" spans="6:6" s="1" customFormat="1">
+    <row r="760" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F760" s="2"/>
     </row>
-    <row r="761" spans="6:6" s="1" customFormat="1">
+    <row r="761" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F761" s="2"/>
     </row>
-    <row r="762" spans="6:6" s="1" customFormat="1">
+    <row r="762" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F762" s="2"/>
     </row>
-    <row r="763" spans="6:6" s="1" customFormat="1">
+    <row r="763" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F763" s="2"/>
     </row>
-    <row r="764" spans="6:6" s="1" customFormat="1">
+    <row r="764" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F764" s="2"/>
     </row>
-    <row r="765" spans="6:6" s="1" customFormat="1">
+    <row r="765" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F765" s="2"/>
     </row>
-    <row r="766" spans="6:6" s="1" customFormat="1">
+    <row r="766" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F766" s="2"/>
     </row>
-    <row r="767" spans="6:6" s="1" customFormat="1">
+    <row r="767" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F767" s="2"/>
     </row>
-    <row r="768" spans="6:6" s="1" customFormat="1">
+    <row r="768" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F768" s="2"/>
     </row>
-    <row r="769" spans="6:6" s="1" customFormat="1">
+    <row r="769" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F769" s="2"/>
     </row>
-    <row r="770" spans="6:6" s="1" customFormat="1">
+    <row r="770" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F770" s="2"/>
     </row>
-    <row r="771" spans="6:6" s="1" customFormat="1">
+    <row r="771" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F771" s="2"/>
     </row>
-    <row r="772" spans="6:6" s="1" customFormat="1">
+    <row r="772" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F772" s="2"/>
     </row>
-    <row r="773" spans="6:6" s="1" customFormat="1">
+    <row r="773" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F773" s="2"/>
     </row>
-    <row r="774" spans="6:6" s="1" customFormat="1">
+    <row r="774" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F774" s="2"/>
     </row>
-    <row r="775" spans="6:6" s="1" customFormat="1">
+    <row r="775" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F775" s="2"/>
     </row>
-    <row r="776" spans="6:6" s="1" customFormat="1">
+    <row r="776" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F776" s="2"/>
     </row>
-    <row r="777" spans="6:6" s="1" customFormat="1">
+    <row r="777" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F777" s="2"/>
     </row>
-    <row r="778" spans="6:6" s="1" customFormat="1">
+    <row r="778" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F778" s="2"/>
     </row>
-    <row r="779" spans="6:6" s="1" customFormat="1">
+    <row r="779" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F779" s="2"/>
     </row>
-    <row r="780" spans="6:6" s="1" customFormat="1">
+    <row r="780" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F780" s="2"/>
     </row>
-    <row r="781" spans="6:6" s="1" customFormat="1">
+    <row r="781" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F781" s="2"/>
     </row>
-    <row r="782" spans="6:6" s="1" customFormat="1">
+    <row r="782" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F782" s="2"/>
     </row>
-    <row r="783" spans="6:6" s="1" customFormat="1">
+    <row r="783" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F783" s="2"/>
     </row>
-    <row r="784" spans="6:6" s="1" customFormat="1">
+    <row r="784" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F784" s="2"/>
     </row>
-    <row r="785" spans="6:6" s="1" customFormat="1">
+    <row r="785" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F785" s="2"/>
     </row>
-    <row r="786" spans="6:6" s="1" customFormat="1">
+    <row r="786" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F786" s="2"/>
     </row>
-    <row r="787" spans="6:6" s="1" customFormat="1">
+    <row r="787" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F787" s="2"/>
     </row>
-    <row r="788" spans="6:6" s="1" customFormat="1">
+    <row r="788" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F788" s="2"/>
     </row>
-    <row r="789" spans="6:6" s="1" customFormat="1">
+    <row r="789" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F789" s="2"/>
     </row>
-    <row r="790" spans="6:6" s="1" customFormat="1">
+    <row r="790" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F790" s="2"/>
     </row>
-    <row r="791" spans="6:6" s="1" customFormat="1">
+    <row r="791" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F791" s="2"/>
     </row>
-    <row r="792" spans="6:6" s="1" customFormat="1">
+    <row r="792" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F792" s="2"/>
     </row>
-    <row r="793" spans="6:6" s="1" customFormat="1">
+    <row r="793" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F793" s="2"/>
     </row>
-    <row r="794" spans="6:6" s="1" customFormat="1">
+    <row r="794" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F794" s="2"/>
     </row>
-    <row r="795" spans="6:6" s="1" customFormat="1">
+    <row r="795" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F795" s="2"/>
     </row>
-    <row r="796" spans="6:6" s="1" customFormat="1">
+    <row r="796" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F796" s="2"/>
     </row>
-    <row r="797" spans="6:6" s="1" customFormat="1">
+    <row r="797" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F797" s="2"/>
     </row>
-    <row r="798" spans="6:6" s="1" customFormat="1">
+    <row r="798" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F798" s="2"/>
     </row>
-    <row r="799" spans="6:6" s="1" customFormat="1">
+    <row r="799" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F799" s="2"/>
     </row>
-    <row r="800" spans="6:6" s="1" customFormat="1">
+    <row r="800" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F800" s="2"/>
     </row>
-    <row r="801" spans="6:6" s="1" customFormat="1">
+    <row r="801" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F801" s="2"/>
     </row>
-    <row r="802" spans="6:6" s="1" customFormat="1">
+    <row r="802" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F802" s="2"/>
     </row>
-    <row r="803" spans="6:6" s="1" customFormat="1">
+    <row r="803" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F803" s="2"/>
     </row>
-    <row r="804" spans="6:6" s="1" customFormat="1">
+    <row r="804" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F804" s="2"/>
     </row>
-    <row r="805" spans="6:6" s="1" customFormat="1">
+    <row r="805" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F805" s="2"/>
     </row>
-    <row r="806" spans="6:6" s="1" customFormat="1">
+    <row r="806" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F806" s="2"/>
     </row>
-    <row r="807" spans="6:6" s="1" customFormat="1">
+    <row r="807" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F807" s="2"/>
     </row>
-    <row r="808" spans="6:6" s="1" customFormat="1">
+    <row r="808" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F808" s="2"/>
     </row>
-    <row r="809" spans="6:6" s="1" customFormat="1">
+    <row r="809" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F809" s="2"/>
     </row>
-    <row r="810" spans="6:6" s="1" customFormat="1">
+    <row r="810" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F810" s="2"/>
     </row>
-    <row r="811" spans="6:6" s="1" customFormat="1">
+    <row r="811" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F811" s="2"/>
     </row>
-    <row r="812" spans="6:6" s="1" customFormat="1">
+    <row r="812" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F812" s="2"/>
     </row>
-    <row r="813" spans="6:6" s="1" customFormat="1">
+    <row r="813" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F813" s="2"/>
     </row>
-    <row r="814" spans="6:6" s="1" customFormat="1">
+    <row r="814" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F814" s="2"/>
     </row>
-    <row r="815" spans="6:6" s="1" customFormat="1">
+    <row r="815" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F815" s="2"/>
     </row>
-    <row r="816" spans="6:6" s="1" customFormat="1">
+    <row r="816" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F816" s="2"/>
     </row>
-    <row r="817" spans="6:6" s="1" customFormat="1">
+    <row r="817" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F817" s="2"/>
     </row>
-    <row r="818" spans="6:6" s="1" customFormat="1">
+    <row r="818" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F818" s="2"/>
     </row>
-    <row r="819" spans="6:6" s="1" customFormat="1">
+    <row r="819" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F819" s="2"/>
     </row>
-    <row r="820" spans="6:6" s="1" customFormat="1">
+    <row r="820" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F820" s="2"/>
     </row>
-    <row r="821" spans="6:6" s="1" customFormat="1">
+    <row r="821" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F821" s="2"/>
     </row>
-    <row r="822" spans="6:6" s="1" customFormat="1">
+    <row r="822" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F822" s="2"/>
     </row>
-    <row r="823" spans="6:6" s="1" customFormat="1">
+    <row r="823" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F823" s="2"/>
     </row>
-    <row r="824" spans="6:6" s="1" customFormat="1">
+    <row r="824" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F824" s="2"/>
     </row>
-    <row r="825" spans="6:6" s="1" customFormat="1">
+    <row r="825" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F825" s="2"/>
     </row>
-    <row r="826" spans="6:6" s="1" customFormat="1">
+    <row r="826" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F826" s="2"/>
     </row>
-    <row r="827" spans="6:6" s="1" customFormat="1">
+    <row r="827" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F827" s="2"/>
     </row>
-    <row r="828" spans="6:6" s="1" customFormat="1">
+    <row r="828" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F828" s="2"/>
     </row>
-    <row r="829" spans="6:6" s="1" customFormat="1">
+    <row r="829" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F829" s="2"/>
     </row>
-    <row r="830" spans="6:6" s="1" customFormat="1">
+    <row r="830" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F830" s="2"/>
     </row>
-    <row r="831" spans="6:6" s="1" customFormat="1">
+    <row r="831" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F831" s="2"/>
     </row>
-    <row r="832" spans="6:6" s="1" customFormat="1">
+    <row r="832" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F832" s="2"/>
     </row>
-    <row r="833" spans="6:6" s="1" customFormat="1">
+    <row r="833" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F833" s="2"/>
     </row>
-    <row r="834" spans="6:6" s="1" customFormat="1">
+    <row r="834" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F834" s="2"/>
     </row>
-    <row r="835" spans="6:6" s="1" customFormat="1">
+    <row r="835" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F835" s="2"/>
     </row>
-    <row r="836" spans="6:6" s="1" customFormat="1">
+    <row r="836" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F836" s="2"/>
     </row>
-    <row r="837" spans="6:6" s="1" customFormat="1">
+    <row r="837" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F837" s="2"/>
     </row>
-    <row r="838" spans="6:6" s="1" customFormat="1">
+    <row r="838" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F838" s="2"/>
     </row>
-    <row r="839" spans="6:6" s="1" customFormat="1">
+    <row r="839" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F839" s="2"/>
     </row>
-    <row r="840" spans="6:6" s="1" customFormat="1">
+    <row r="840" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F840" s="2"/>
     </row>
-    <row r="841" spans="6:6" s="1" customFormat="1">
+    <row r="841" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F841" s="2"/>
     </row>
-    <row r="842" spans="6:6" s="1" customFormat="1">
+    <row r="842" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F842" s="2"/>
     </row>
-    <row r="843" spans="6:6" s="1" customFormat="1">
+    <row r="843" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F843" s="2"/>
     </row>
-    <row r="844" spans="6:6" s="1" customFormat="1">
+    <row r="844" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F844" s="2"/>
     </row>
-    <row r="845" spans="6:6" s="1" customFormat="1">
+    <row r="845" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F845" s="2"/>
     </row>
-    <row r="846" spans="6:6" s="1" customFormat="1">
+    <row r="846" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F846" s="2"/>
     </row>
-    <row r="847" spans="6:6" s="1" customFormat="1">
+    <row r="847" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F847" s="2"/>
     </row>
-    <row r="848" spans="6:6" s="1" customFormat="1">
+    <row r="848" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F848" s="2"/>
     </row>
-    <row r="849" spans="6:6" s="1" customFormat="1">
+    <row r="849" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F849" s="2"/>
     </row>
-    <row r="850" spans="6:6" s="1" customFormat="1">
+    <row r="850" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F850" s="2"/>
     </row>
-    <row r="851" spans="6:6" s="1" customFormat="1">
+    <row r="851" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F851" s="2"/>
     </row>
-    <row r="852" spans="6:6" s="1" customFormat="1">
+    <row r="852" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F852" s="2"/>
     </row>
-    <row r="853" spans="6:6" s="1" customFormat="1">
+    <row r="853" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F853" s="2"/>
     </row>
-    <row r="854" spans="6:6" s="1" customFormat="1">
+    <row r="854" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F854" s="2"/>
     </row>
-    <row r="855" spans="6:6" s="1" customFormat="1">
+    <row r="855" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F855" s="2"/>
     </row>
-    <row r="856" spans="6:6" s="1" customFormat="1">
+    <row r="856" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F856" s="2"/>
     </row>
-    <row r="857" spans="6:6" s="1" customFormat="1">
+    <row r="857" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F857" s="2"/>
     </row>
-    <row r="858" spans="6:6" s="1" customFormat="1">
+    <row r="858" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F858" s="2"/>
     </row>
-    <row r="859" spans="6:6" s="1" customFormat="1">
+    <row r="859" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F859" s="2"/>
     </row>
-    <row r="860" spans="6:6" s="1" customFormat="1">
+    <row r="860" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F860" s="2"/>
     </row>
-    <row r="861" spans="6:6" s="1" customFormat="1">
+    <row r="861" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F861" s="2"/>
     </row>
-    <row r="862" spans="6:6" s="1" customFormat="1">
+    <row r="862" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F862" s="2"/>
     </row>
-    <row r="863" spans="6:6" s="1" customFormat="1">
+    <row r="863" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F863" s="2"/>
     </row>
-    <row r="864" spans="6:6" s="1" customFormat="1">
+    <row r="864" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F864" s="2"/>
     </row>
-    <row r="865" spans="6:6" s="1" customFormat="1">
+    <row r="865" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F865" s="2"/>
     </row>
-    <row r="866" spans="6:6" s="1" customFormat="1">
+    <row r="866" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F866" s="2"/>
     </row>
-    <row r="867" spans="6:6" s="1" customFormat="1">
+    <row r="867" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F867" s="2"/>
     </row>
-    <row r="868" spans="6:6" s="1" customFormat="1">
+    <row r="868" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F868" s="2"/>
     </row>
-    <row r="869" spans="6:6" s="1" customFormat="1">
+    <row r="869" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F869" s="2"/>
     </row>
-    <row r="870" spans="6:6" s="1" customFormat="1">
+    <row r="870" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F870" s="2"/>
     </row>
-    <row r="871" spans="6:6" s="1" customFormat="1">
+    <row r="871" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F871" s="2"/>
     </row>
-    <row r="872" spans="6:6" s="1" customFormat="1">
+    <row r="872" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F872" s="2"/>
     </row>
-    <row r="873" spans="6:6" s="1" customFormat="1">
+    <row r="873" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F873" s="2"/>
     </row>
-    <row r="874" spans="6:6" s="1" customFormat="1">
+    <row r="874" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F874" s="2"/>
     </row>
-    <row r="875" spans="6:6" s="1" customFormat="1">
+    <row r="875" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F875" s="2"/>
     </row>
-    <row r="876" spans="6:6" s="1" customFormat="1">
+    <row r="876" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F876" s="2"/>
     </row>
-    <row r="877" spans="6:6" s="1" customFormat="1">
+    <row r="877" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F877" s="2"/>
     </row>
-    <row r="878" spans="6:6" s="1" customFormat="1">
+    <row r="878" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F878" s="2"/>
     </row>
-    <row r="879" spans="6:6" s="1" customFormat="1">
+    <row r="879" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F879" s="2"/>
     </row>
-    <row r="880" spans="6:6" s="1" customFormat="1">
+    <row r="880" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F880" s="2"/>
     </row>
-    <row r="881" spans="6:6" s="1" customFormat="1">
+    <row r="881" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F881" s="2"/>
     </row>
-    <row r="882" spans="6:6" s="1" customFormat="1">
+    <row r="882" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F882" s="2"/>
     </row>
-    <row r="883" spans="6:6" s="1" customFormat="1">
+    <row r="883" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F883" s="2"/>
     </row>
-    <row r="884" spans="6:6" s="1" customFormat="1">
+    <row r="884" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F884" s="2"/>
     </row>
-    <row r="885" spans="6:6" s="1" customFormat="1">
+    <row r="885" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F885" s="2"/>
     </row>
-    <row r="886" spans="6:6" s="1" customFormat="1">
+    <row r="886" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F886" s="2"/>
     </row>
-    <row r="887" spans="6:6" s="1" customFormat="1">
+    <row r="887" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F887" s="2"/>
     </row>
-    <row r="888" spans="6:6" s="1" customFormat="1">
+    <row r="888" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F888" s="2"/>
     </row>
-    <row r="889" spans="6:6" s="1" customFormat="1">
+    <row r="889" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F889" s="2"/>
     </row>
-    <row r="890" spans="6:6" s="1" customFormat="1">
+    <row r="890" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F890" s="2"/>
     </row>
-    <row r="891" spans="6:6" s="1" customFormat="1">
+    <row r="891" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F891" s="2"/>
     </row>
-    <row r="892" spans="6:6" s="1" customFormat="1">
+    <row r="892" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F892" s="2"/>
     </row>
-    <row r="893" spans="6:6" s="1" customFormat="1">
+    <row r="893" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F893" s="2"/>
     </row>
-    <row r="894" spans="6:6" s="1" customFormat="1">
+    <row r="894" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F894" s="2"/>
     </row>
-    <row r="895" spans="6:6" s="1" customFormat="1">
+    <row r="895" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F895" s="2"/>
     </row>
-    <row r="896" spans="6:6" s="1" customFormat="1">
+    <row r="896" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F896" s="2"/>
     </row>
-    <row r="897" spans="6:6" s="1" customFormat="1">
+    <row r="897" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F897" s="2"/>
     </row>
-    <row r="898" spans="6:6" s="1" customFormat="1">
+    <row r="898" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F898" s="2"/>
     </row>
-    <row r="899" spans="6:6" s="1" customFormat="1">
+    <row r="899" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F899" s="2"/>
     </row>
-    <row r="900" spans="6:6" s="1" customFormat="1">
+    <row r="900" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F900" s="2"/>
     </row>
-    <row r="901" spans="6:6" s="1" customFormat="1">
+    <row r="901" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F901" s="2"/>
     </row>
-    <row r="902" spans="6:6" s="1" customFormat="1">
+    <row r="902" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F902" s="2"/>
     </row>
-    <row r="903" spans="6:6" s="1" customFormat="1">
+    <row r="903" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F903" s="2"/>
     </row>
-    <row r="904" spans="6:6" s="1" customFormat="1">
+    <row r="904" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F904" s="2"/>
     </row>
-    <row r="905" spans="6:6" s="1" customFormat="1">
+    <row r="905" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F905" s="2"/>
     </row>
-    <row r="906" spans="6:6" s="1" customFormat="1">
+    <row r="906" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F906" s="2"/>
     </row>
-    <row r="907" spans="6:6" s="1" customFormat="1">
+    <row r="907" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F907" s="2"/>
     </row>
-    <row r="908" spans="6:6" s="1" customFormat="1">
+    <row r="908" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F908" s="2"/>
     </row>
-    <row r="909" spans="6:6" s="1" customFormat="1">
+    <row r="909" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F909" s="2"/>
     </row>
-    <row r="910" spans="6:6" s="1" customFormat="1">
+    <row r="910" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F910" s="2"/>
     </row>
-    <row r="911" spans="6:6" s="1" customFormat="1">
+    <row r="911" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F911" s="2"/>
     </row>
-    <row r="912" spans="6:6" s="1" customFormat="1">
+    <row r="912" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F912" s="2"/>
     </row>
-    <row r="913" spans="6:6" s="1" customFormat="1">
+    <row r="913" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F913" s="2"/>
     </row>
-    <row r="914" spans="6:6" s="1" customFormat="1">
+    <row r="914" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F914" s="2"/>
     </row>
-    <row r="915" spans="6:6" s="1" customFormat="1">
+    <row r="915" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F915" s="2"/>
     </row>
-    <row r="916" spans="6:6" s="1" customFormat="1">
+    <row r="916" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F916" s="2"/>
     </row>
-    <row r="917" spans="6:6" s="1" customFormat="1">
+    <row r="917" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F917" s="2"/>
     </row>
-    <row r="918" spans="6:6" s="1" customFormat="1">
+    <row r="918" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F918" s="2"/>
     </row>
-    <row r="919" spans="6:6" s="1" customFormat="1">
+    <row r="919" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F919" s="2"/>
     </row>
-    <row r="920" spans="6:6" s="1" customFormat="1">
+    <row r="920" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F920" s="2"/>
     </row>
-    <row r="921" spans="6:6" s="1" customFormat="1">
+    <row r="921" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F921" s="2"/>
     </row>
-    <row r="922" spans="6:6" s="1" customFormat="1">
+    <row r="922" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F922" s="2"/>
     </row>
-    <row r="923" spans="6:6" s="1" customFormat="1">
+    <row r="923" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F923" s="2"/>
     </row>
-    <row r="924" spans="6:6" s="1" customFormat="1">
+    <row r="924" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F924" s="2"/>
     </row>
-    <row r="925" spans="6:6" s="1" customFormat="1">
+    <row r="925" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F925" s="2"/>
     </row>
-    <row r="926" spans="6:6" s="1" customFormat="1">
+    <row r="926" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F926" s="2"/>
     </row>
-    <row r="927" spans="6:6" s="1" customFormat="1">
+    <row r="927" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F927" s="2"/>
     </row>
-    <row r="928" spans="6:6" s="1" customFormat="1">
+    <row r="928" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F928" s="2"/>
     </row>
-    <row r="929" spans="6:6" s="1" customFormat="1">
+    <row r="929" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F929" s="2"/>
     </row>
-    <row r="930" spans="6:6" s="1" customFormat="1">
+    <row r="930" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F930" s="2"/>
     </row>
-    <row r="931" spans="6:6" s="1" customFormat="1">
+    <row r="931" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F931" s="2"/>
     </row>
-    <row r="932" spans="6:6" s="1" customFormat="1">
+    <row r="932" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F932" s="2"/>
     </row>
-    <row r="933" spans="6:6" s="1" customFormat="1">
+    <row r="933" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F933" s="2"/>
     </row>
-    <row r="934" spans="6:6" s="1" customFormat="1">
+    <row r="934" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F934" s="2"/>
     </row>
-    <row r="935" spans="6:6" s="1" customFormat="1">
+    <row r="935" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F935" s="2"/>
     </row>
-    <row r="936" spans="6:6" s="1" customFormat="1">
+    <row r="936" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F936" s="2"/>
     </row>
-    <row r="937" spans="6:6" s="1" customFormat="1">
+    <row r="937" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F937" s="2"/>
     </row>
-    <row r="938" spans="6:6" s="1" customFormat="1">
+    <row r="938" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F938" s="2"/>
     </row>
-    <row r="939" spans="6:6" s="1" customFormat="1">
+    <row r="939" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F939" s="2"/>
     </row>
-    <row r="940" spans="6:6" s="1" customFormat="1">
+    <row r="940" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F940" s="2"/>
     </row>
-    <row r="941" spans="6:6" s="1" customFormat="1">
+    <row r="941" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F941" s="2"/>
     </row>
-    <row r="942" spans="6:6" s="1" customFormat="1">
+    <row r="942" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F942" s="2"/>
     </row>
-    <row r="943" spans="6:6" s="1" customFormat="1">
+    <row r="943" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F943" s="2"/>
     </row>
-    <row r="944" spans="6:6" s="1" customFormat="1">
+    <row r="944" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F944" s="2"/>
     </row>
-    <row r="945" spans="6:6" s="1" customFormat="1">
+    <row r="945" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F945" s="2"/>
     </row>
-    <row r="946" spans="6:6" s="1" customFormat="1">
+    <row r="946" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F946" s="2"/>
     </row>
-    <row r="947" spans="6:6" s="1" customFormat="1">
+    <row r="947" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F947" s="2"/>
     </row>
-    <row r="948" spans="6:6" s="1" customFormat="1">
+    <row r="948" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F948" s="2"/>
     </row>
-    <row r="949" spans="6:6" s="1" customFormat="1">
+    <row r="949" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F949" s="2"/>
     </row>
-    <row r="950" spans="6:6" s="1" customFormat="1">
+    <row r="950" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F950" s="2"/>
     </row>
-    <row r="951" spans="6:6" s="1" customFormat="1">
+    <row r="951" spans="6:6" s="1" customFormat="1" ht="12.000000">
       <c r="F951" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="D29:J29"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:J26"/>
-    <mergeCell ref="A27:C28"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:J25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="D24:J24"/>
-    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="H12:J12"/>
     <mergeCell ref="F13:I13"/>
@@ -5577,47 +5994,51 @@
     <mergeCell ref="E15:H15"/>
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="E17:H17"/>
-    <mergeCell ref="E21:H21"/>
     <mergeCell ref="E18:H18"/>
     <mergeCell ref="E19:H19"/>
     <mergeCell ref="E20:H20"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:J25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D26:J26"/>
+    <mergeCell ref="A27:C28"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D29:J29"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.75" right="0.71" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.71" top="1.00" bottom="1.00" header="0.50" footer="0.50"/>
   <pageSetup paperSize="9" scale="78" orientation="portrait"/>
-  <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2AC3E23-57FD-DF41-9734-F410846F4223}">
-  <dimension ref="A1:K62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.500000"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" style="33" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" style="33" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" style="33" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" style="33" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" style="33" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" style="33" customWidth="1"/>
-    <col min="8" max="8" width="11.1640625" style="33" customWidth="1"/>
-    <col min="9" max="9" width="7.5" style="33" customWidth="1"/>
-    <col min="10" max="10" width="4.5" style="33" customWidth="1"/>
-    <col min="11" max="11" width="10" style="33" customWidth="1"/>
-    <col min="12" max="12" width="7.1640625" style="33" customWidth="1"/>
-    <col min="13" max="16384" width="8.83203125" style="33"/>
+    <col min="1" max="1" style="33" width="9.11611101" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="2" style="33" width="11.11611101" customWidth="1" outlineLevel="0"/>
+    <col min="3" max="3" style="33" width="8.33833334" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="4" style="33" width="10.11611101" customWidth="1" outlineLevel="0"/>
+    <col min="5" max="5" style="33" width="16.78277800" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="6" style="33" width="10.11611101" customWidth="1" outlineLevel="0"/>
+    <col min="7" max="7" style="33" width="8.67166636" customWidth="1" outlineLevel="0"/>
+    <col min="8" max="8" style="33" width="11.11611101" customWidth="1" outlineLevel="0"/>
+    <col min="9" max="9" style="33" width="7.44944451" customWidth="1" outlineLevel="0"/>
+    <col min="10" max="10" style="33" width="4.44944451" customWidth="1" outlineLevel="0"/>
+    <col min="11" max="11" style="33" width="10.00500033" customWidth="1" outlineLevel="0"/>
+    <col min="12" max="12" style="33" width="7.11611101" customWidth="1" outlineLevel="0"/>
+    <col min="13" max="16384" style="33" width="8.78277800" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -5627,70 +6048,70 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A2" s="157" t="s">
+    <row r="2" spans="1:11" ht="26.250000" customHeight="1">
+      <c r="A2" s="152" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="157"/>
+      <c r="B2" s="152"/>
       <c r="C2" s="36"/>
       <c r="D2" s="36"/>
       <c r="E2" s="36"/>
       <c r="F2" s="36"/>
     </row>
-    <row r="3" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
+    <row r="3" spans="1:11" ht="15.750000" customHeight="1">
       <c r="C3" s="34"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-    </row>
-    <row r="4" spans="1:11" ht="32" customHeight="1">
-      <c r="A4" s="159" t="s">
+      <c r="H3" s="153"/>
+      <c r="I3" s="153"/>
+    </row>
+    <row r="4" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A4" s="154" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="161" t="s">
+      <c r="B4" s="156" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="161" t="s">
+      <c r="C4" s="156" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="161"/>
-      <c r="E4" s="161"/>
-      <c r="F4" s="161" t="s">
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="161" t="s">
+      <c r="G4" s="156" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="161" t="s">
+      <c r="H4" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="163" t="s">
+      <c r="I4" s="157" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="32" customHeight="1" thickBot="1">
-      <c r="A5" s="160"/>
-      <c r="B5" s="162"/>
-      <c r="C5" s="137" t="s">
+    <row r="5" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A5" s="155"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="135" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="138"/>
+      <c r="D5" s="136"/>
       <c r="E5" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="162"/>
-      <c r="G5" s="162"/>
-      <c r="H5" s="162"/>
-      <c r="I5" s="164"/>
-    </row>
-    <row r="6" spans="1:11" ht="32" customHeight="1" thickTop="1">
-      <c r="A6" s="153" t="s">
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="158"/>
+    </row>
+    <row r="6" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A6" s="148" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="151"/>
-      <c r="D6" s="152"/>
+      <c r="C6" s="146"/>
+      <c r="D6" s="147"/>
       <c r="E6" s="38"/>
       <c r="F6" s="38">
         <f>C6+E6</f>
@@ -5705,73 +6126,73 @@
       </c>
       <c r="I6" s="79"/>
     </row>
-    <row r="7" spans="1:11" ht="32" customHeight="1">
-      <c r="A7" s="154"/>
+    <row r="7" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A7" s="149"/>
       <c r="B7" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="139"/>
-      <c r="D7" s="140"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="138"/>
       <c r="E7" s="38"/>
       <c r="F7" s="38">
-        <f t="shared" ref="F7:F9" si="0">C7+E7</f>
+        <f>C7+E7</f>
         <v>0</v>
       </c>
       <c r="G7" s="39"/>
       <c r="H7" s="39">
-        <f t="shared" ref="H7:H9" si="1">G7*F7</f>
+        <f>G7*F7</f>
         <v>0</v>
       </c>
       <c r="I7" s="40"/>
     </row>
-    <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="154"/>
+    <row r="8" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A8" s="149"/>
       <c r="B8" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="139"/>
-      <c r="D8" s="140"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="138"/>
       <c r="E8" s="38"/>
       <c r="F8" s="38">
-        <f t="shared" si="0"/>
+        <f>C8+E8</f>
         <v>0</v>
       </c>
       <c r="G8" s="39"/>
       <c r="H8" s="39">
-        <f t="shared" si="1"/>
+        <f>G8*F8</f>
         <v>0</v>
       </c>
       <c r="I8" s="40"/>
     </row>
-    <row r="9" spans="1:11" ht="32" customHeight="1">
-      <c r="A9" s="155"/>
+    <row r="9" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A9" s="150"/>
       <c r="B9" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="139"/>
-      <c r="D9" s="140"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="138"/>
       <c r="E9" s="38"/>
       <c r="F9" s="38">
-        <f t="shared" si="0"/>
+        <f>C9+E9</f>
         <v>0</v>
       </c>
       <c r="G9" s="39"/>
       <c r="H9" s="39">
-        <f t="shared" si="1"/>
+        <f>G9*F9</f>
         <v>0</v>
       </c>
       <c r="I9" s="40"/>
     </row>
-    <row r="10" spans="1:11" ht="32" customHeight="1">
-      <c r="A10" s="156"/>
+    <row r="10" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A10" s="151"/>
       <c r="B10" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="141">
+      <c r="C10" s="44">
         <f>SUM(C6:D9)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="142"/>
+      <c r="D10" s="139"/>
       <c r="E10" s="38">
         <f>SUM(E6:E9)</f>
         <v>0</v>
@@ -5789,8 +6210,8 @@
       </c>
       <c r="I10" s="40"/>
     </row>
-    <row r="11" spans="1:11" ht="32" customHeight="1">
-      <c r="A11" s="165" t="s">
+    <row r="11" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A11" s="42" t="s">
         <v>30</v>
       </c>
       <c r="B11" s="43" t="s">
@@ -5812,8 +6233,8 @@
       </c>
       <c r="I11" s="47"/>
     </row>
-    <row r="12" spans="1:11" ht="32" customHeight="1">
-      <c r="A12" s="166"/>
+    <row r="12" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A12" s="159"/>
       <c r="B12" s="43" t="s">
         <v>51</v>
       </c>
@@ -5832,8 +6253,8 @@
       </c>
       <c r="I12" s="47"/>
     </row>
-    <row r="13" spans="1:11" ht="32" customHeight="1">
-      <c r="A13" s="166"/>
+    <row r="13" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A13" s="159"/>
       <c r="B13" s="43" t="s">
         <v>50</v>
       </c>
@@ -5853,8 +6274,8 @@
       </c>
       <c r="I13" s="47"/>
     </row>
-    <row r="14" spans="1:11" ht="32" customHeight="1">
-      <c r="A14" s="166"/>
+    <row r="14" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A14" s="159"/>
       <c r="B14" s="43" t="s">
         <v>52</v>
       </c>
@@ -5873,44 +6294,44 @@
       </c>
       <c r="I14" s="49"/>
     </row>
-    <row r="15" spans="1:11" ht="32" customHeight="1">
-      <c r="A15" s="166"/>
+    <row r="15" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A15" s="159"/>
       <c r="B15" s="43" t="s">
         <v>53</v>
       </c>
       <c r="C15" s="50"/>
       <c r="D15" s="51"/>
       <c r="E15" s="52"/>
-      <c r="F15" s="174">
+      <c r="F15" s="167">
         <v>0</v>
       </c>
-      <c r="G15" s="175"/>
+      <c r="G15" s="168"/>
       <c r="H15" s="46">
-        <f>ROUND(H10*(F15*0.01), 0)</f>
+        <f>ROUND(H10*(F15*0.01),0)</f>
         <v>0</v>
       </c>
       <c r="I15" s="47"/>
     </row>
-    <row r="16" spans="1:11" ht="32" customHeight="1">
-      <c r="A16" s="166"/>
+    <row r="16" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A16" s="159"/>
       <c r="B16" s="43" t="s">
         <v>54</v>
       </c>
       <c r="C16" s="53"/>
       <c r="D16" s="54"/>
       <c r="E16" s="55"/>
-      <c r="F16" s="174">
+      <c r="F16" s="167">
         <v>0</v>
       </c>
-      <c r="G16" s="175"/>
+      <c r="G16" s="168"/>
       <c r="H16" s="46">
-        <f>ROUND(H10*(F16*0.01), 0)</f>
+        <f>ROUND(H10*(F16*0.01),0)</f>
         <v>0</v>
       </c>
       <c r="I16" s="56"/>
     </row>
-    <row r="17" spans="1:11" ht="32" customHeight="1">
-      <c r="A17" s="166"/>
+    <row r="17" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A17" s="159"/>
       <c r="B17" s="43" t="s">
         <v>55</v>
       </c>
@@ -5929,8 +6350,8 @@
       </c>
       <c r="I17" s="47"/>
     </row>
-    <row r="18" spans="1:11" ht="32" customHeight="1">
-      <c r="A18" s="166"/>
+    <row r="18" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A18" s="159"/>
       <c r="B18" s="57" t="s">
         <v>31</v>
       </c>
@@ -5945,152 +6366,152 @@
       </c>
       <c r="I18" s="62"/>
     </row>
-    <row r="19" spans="1:11" ht="32" customHeight="1">
+    <row r="19" spans="1:11" ht="32.000000" customHeight="1">
       <c r="A19" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="170">
+      <c r="B19" s="163">
         <v>0</v>
       </c>
-      <c r="C19" s="170"/>
-      <c r="D19" s="170"/>
-      <c r="E19" s="170"/>
-      <c r="F19" s="170"/>
-      <c r="G19" s="170"/>
+      <c r="C19" s="163"/>
+      <c r="D19" s="163"/>
+      <c r="E19" s="163"/>
+      <c r="F19" s="163"/>
+      <c r="G19" s="163"/>
       <c r="H19" s="46">
         <f>ROUND(H10*(B19*0.01),0)</f>
         <v>0</v>
       </c>
       <c r="I19" s="47"/>
     </row>
-    <row r="20" spans="1:11" ht="32" customHeight="1">
+    <row r="20" spans="1:11" ht="32.000000" customHeight="1">
       <c r="A20" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="171">
+      <c r="B20" s="164">
         <v>0</v>
       </c>
-      <c r="C20" s="172"/>
-      <c r="D20" s="172"/>
-      <c r="E20" s="172"/>
-      <c r="F20" s="172"/>
-      <c r="G20" s="173"/>
+      <c r="C20" s="165"/>
+      <c r="D20" s="165"/>
+      <c r="E20" s="165"/>
+      <c r="F20" s="165"/>
+      <c r="G20" s="166"/>
       <c r="H20" s="46">
         <f>ROUND((H10+H19)*(B20*0.01),0)</f>
         <v>0</v>
       </c>
       <c r="I20" s="47"/>
     </row>
-    <row r="21" spans="1:11" ht="32" customHeight="1">
+    <row r="21" spans="1:11" ht="32.000000" customHeight="1">
       <c r="A21" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="148" t="s">
+      <c r="B21" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="149"/>
-      <c r="D21" s="149"/>
-      <c r="E21" s="149"/>
-      <c r="F21" s="149"/>
-      <c r="G21" s="150"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="145"/>
       <c r="H21" s="61">
         <f>H10+H18+H19+H20</f>
         <v>50000</v>
       </c>
       <c r="I21" s="62"/>
     </row>
-    <row r="22" spans="1:11" ht="32" customHeight="1">
-      <c r="A22" s="165" t="s">
+    <row r="22" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A22" s="42" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="43"/>
-      <c r="C22" s="167" t="s">
+      <c r="C22" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="168"/>
-      <c r="E22" s="168"/>
-      <c r="F22" s="168"/>
-      <c r="G22" s="169"/>
+      <c r="D22" s="161"/>
+      <c r="E22" s="161"/>
+      <c r="F22" s="161"/>
+      <c r="G22" s="162"/>
       <c r="H22" s="46">
         <v>0</v>
       </c>
       <c r="I22" s="47"/>
     </row>
-    <row r="23" spans="1:11" ht="32" customHeight="1">
-      <c r="A23" s="166"/>
+    <row r="23" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A23" s="159"/>
       <c r="B23" s="43"/>
-      <c r="C23" s="167" t="s">
+      <c r="C23" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="168"/>
-      <c r="E23" s="168"/>
-      <c r="F23" s="168"/>
-      <c r="G23" s="169"/>
+      <c r="D23" s="161"/>
+      <c r="E23" s="161"/>
+      <c r="F23" s="161"/>
+      <c r="G23" s="162"/>
       <c r="H23" s="46">
         <v>0</v>
       </c>
       <c r="I23" s="47"/>
     </row>
-    <row r="24" spans="1:11" ht="32" customHeight="1">
-      <c r="A24" s="166"/>
+    <row r="24" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A24" s="159"/>
       <c r="B24" s="64"/>
-      <c r="C24" s="167" t="s">
+      <c r="C24" s="160" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="168"/>
-      <c r="E24" s="168"/>
-      <c r="F24" s="168"/>
-      <c r="G24" s="169"/>
+      <c r="D24" s="161"/>
+      <c r="E24" s="161"/>
+      <c r="F24" s="161"/>
+      <c r="G24" s="162"/>
       <c r="H24" s="46">
         <v>0</v>
       </c>
       <c r="I24" s="65"/>
     </row>
-    <row r="25" spans="1:11" ht="32" customHeight="1">
-      <c r="A25" s="166"/>
+    <row r="25" spans="1:11" ht="32.000000" customHeight="1">
+      <c r="A25" s="159"/>
       <c r="B25" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="167" t="s">
+      <c r="C25" s="160" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="168"/>
-      <c r="E25" s="168"/>
-      <c r="F25" s="168"/>
-      <c r="G25" s="169"/>
+      <c r="D25" s="161"/>
+      <c r="E25" s="161"/>
+      <c r="F25" s="161"/>
+      <c r="G25" s="162"/>
       <c r="H25" s="61">
         <f>SUM(H22:H24)</f>
         <v>0</v>
       </c>
       <c r="I25" s="62"/>
     </row>
-    <row r="26" spans="1:11" ht="32" customHeight="1">
+    <row r="26" spans="1:11" ht="32.000000" customHeight="1">
       <c r="A26" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="145" t="s">
+      <c r="B26" s="142" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="146"/>
-      <c r="D26" s="146"/>
-      <c r="E26" s="146"/>
-      <c r="F26" s="146"/>
-      <c r="G26" s="147"/>
+      <c r="C26" s="143"/>
+      <c r="D26" s="143"/>
+      <c r="E26" s="143"/>
+      <c r="F26" s="143"/>
+      <c r="G26" s="144"/>
       <c r="H26" s="67">
         <f>H25+H21</f>
         <v>50000</v>
       </c>
       <c r="I26" s="68"/>
     </row>
-    <row r="27" spans="1:11" ht="32" customHeight="1" thickBot="1">
+    <row r="27" spans="1:11" ht="32.000000" customHeight="1">
       <c r="A27" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="143">
+      <c r="B27" s="140">
         <f>H26</f>
         <v>50000</v>
       </c>
-      <c r="C27" s="144"/>
+      <c r="C27" s="141"/>
       <c r="D27" s="76">
         <v>1</v>
       </c>
@@ -6098,65 +6519,54 @@
         <f>B27*D27</f>
         <v>50000</v>
       </c>
-      <c r="F27" s="135"/>
-      <c r="G27" s="136"/>
+      <c r="F27" s="133"/>
+      <c r="G27" s="134"/>
       <c r="H27" s="70"/>
       <c r="I27" s="78" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="30" customHeight="1"/>
-    <row r="29" spans="1:11" ht="30" customHeight="1">
+    <row r="28" ht="30.000000" customHeight="1"/>
+    <row r="29" spans="1:11" ht="30.000000" customHeight="1">
       <c r="K29" s="71"/>
     </row>
-    <row r="30" spans="1:11" ht="30" customHeight="1">
+    <row r="30" spans="1:11" ht="30.000000" customHeight="1">
       <c r="H30" s="71"/>
     </row>
-    <row r="31" spans="1:11" ht="30" customHeight="1"/>
-    <row r="32" spans="1:11" ht="30" customHeight="1"/>
-    <row r="33" ht="30" customHeight="1"/>
-    <row r="34" ht="30" customHeight="1"/>
-    <row r="35" ht="30" customHeight="1"/>
-    <row r="36" ht="30" customHeight="1"/>
-    <row r="37" ht="30" customHeight="1"/>
-    <row r="38" ht="30" customHeight="1"/>
-    <row r="39" ht="30" customHeight="1"/>
-    <row r="40" ht="30" customHeight="1"/>
-    <row r="41" ht="30" customHeight="1"/>
-    <row r="42" ht="30" customHeight="1"/>
-    <row r="43" ht="30" customHeight="1"/>
-    <row r="44" ht="30" customHeight="1"/>
-    <row r="45" ht="30" customHeight="1"/>
-    <row r="46" ht="30" customHeight="1"/>
-    <row r="47" ht="30" customHeight="1"/>
-    <row r="48" ht="30" customHeight="1"/>
-    <row r="49" ht="30" customHeight="1"/>
-    <row r="50" ht="30" customHeight="1"/>
-    <row r="51" ht="30" customHeight="1"/>
-    <row r="52" ht="30" customHeight="1"/>
-    <row r="53" ht="30" customHeight="1"/>
-    <row r="54" ht="30" customHeight="1"/>
-    <row r="55" ht="30" customHeight="1"/>
-    <row r="56" ht="30" customHeight="1"/>
-    <row r="57" ht="30" customHeight="1"/>
-    <row r="58" ht="30" customHeight="1"/>
-    <row r="59" ht="30" customHeight="1"/>
-    <row r="60" ht="30" customHeight="1"/>
-    <row r="61" ht="30" customHeight="1"/>
-    <row r="62" ht="30" customHeight="1"/>
+    <row r="31" ht="30.000000" customHeight="1"/>
+    <row r="32" ht="30.000000" customHeight="1"/>
+    <row r="33" ht="30.000000" customHeight="1"/>
+    <row r="34" ht="30.000000" customHeight="1"/>
+    <row r="35" ht="30.000000" customHeight="1"/>
+    <row r="36" ht="30.000000" customHeight="1"/>
+    <row r="37" ht="30.000000" customHeight="1"/>
+    <row r="38" ht="30.000000" customHeight="1"/>
+    <row r="39" ht="30.000000" customHeight="1"/>
+    <row r="40" ht="30.000000" customHeight="1"/>
+    <row r="41" ht="30.000000" customHeight="1"/>
+    <row r="42" ht="30.000000" customHeight="1"/>
+    <row r="43" ht="30.000000" customHeight="1"/>
+    <row r="44" ht="30.000000" customHeight="1"/>
+    <row r="45" ht="30.000000" customHeight="1"/>
+    <row r="46" ht="30.000000" customHeight="1"/>
+    <row r="47" ht="30.000000" customHeight="1"/>
+    <row r="48" ht="30.000000" customHeight="1"/>
+    <row r="49" ht="30.000000" customHeight="1"/>
+    <row r="50" ht="30.000000" customHeight="1"/>
+    <row r="51" ht="30.000000" customHeight="1"/>
+    <row r="52" ht="30.000000" customHeight="1"/>
+    <row r="53" ht="30.000000" customHeight="1"/>
+    <row r="54" ht="30.000000" customHeight="1"/>
+    <row r="55" ht="30.000000" customHeight="1"/>
+    <row r="56" ht="30.000000" customHeight="1"/>
+    <row r="57" ht="30.000000" customHeight="1"/>
+    <row r="58" ht="30.000000" customHeight="1"/>
+    <row r="59" ht="30.000000" customHeight="1"/>
+    <row r="60" ht="30.000000" customHeight="1"/>
+    <row r="61" ht="30.000000" customHeight="1"/>
+    <row r="62" ht="30.000000" customHeight="1"/>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A11:A18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="A6:A10"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="H3:I3"/>
     <mergeCell ref="A4:A5"/>
@@ -6166,21 +6576,31 @@
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C5:D5"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:A18"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="F27:G27"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.72" right="0.71" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageMargins left="0.72" right="0.71" top="0.98" bottom="0.98" header="0.51" footer="0.51"/>
   <pageSetup paperSize="9" scale="81" orientation="portrait"/>
-  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>